--- a/nbs/files/lut/dbo_lab_cleaned.xlsx
+++ b/nbs/files/lut/dbo_lab_cleaned.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/franckalbinet/pro/IAEA/MARIS/marisco/nbs/files/lut/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B950EF-CED3-EA46-824C-1CE56CB34AE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="2505" windowWidth="21600" windowHeight="12735"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="dbo_lab" sheetId="1" r:id="rId1"/>
@@ -12,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">dbo_lab!$A$1:$K$519</definedName>
   </definedNames>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2143" uniqueCount="1610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2145" uniqueCount="1612">
   <si>
     <t>lab_id</t>
   </si>
@@ -4864,12 +4870,18 @@
   </si>
   <si>
     <t xml:space="preserve"> Ruder Boskovic  Institute Centre for Marine Research</t>
+  </si>
+  <si>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>Vienna Environmental Research Accelerator facility at the University of Vienna, Austria</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -5229,27 +5241,27 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N502"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N503"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.140625" customWidth="1"/>
-    <col min="2" max="2" width="13.42578125" customWidth="1"/>
-    <col min="3" max="3" width="136.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.42578125" customWidth="1"/>
-    <col min="6" max="6" width="27.42578125" customWidth="1"/>
+    <col min="1" max="1" width="14.1640625" customWidth="1"/>
+    <col min="2" max="2" width="13.5" customWidth="1"/>
+    <col min="3" max="3" width="136.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.5" customWidth="1"/>
+    <col min="6" max="6" width="27.5" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="52.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="52.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5284,7 +5296,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>-1</v>
       </c>
@@ -5295,7 +5307,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>0</v>
       </c>
@@ -5310,7 +5322,7 @@
       </c>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
@@ -5330,11 +5342,11 @@
         <v>15</v>
       </c>
       <c r="N4" t="str">
-        <f>"update lab set lab =  " &amp;C4&amp; " , country =  "&amp;H4&amp;"  where lab_id = "&amp;A4</f>
+        <f t="shared" ref="N4:N67" si="0">"update lab set lab =  " &amp;C4&amp; " , country =  "&amp;H4&amp;"  where lab_id = "&amp;A4</f>
         <v>update lab set lab =  International Atomic Energy Agency - Environment Laboratory _former Marine Environment Laboratory_ , country =    where lab_id = 1</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2</v>
       </c>
@@ -5351,11 +5363,11 @@
         <v>19</v>
       </c>
       <c r="N5" t="str">
-        <f>"update lab set lab =  " &amp;C5&amp; " , country =  "&amp;H5&amp;"  where lab_id = "&amp;A5</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Institute of Nuclear Physics - Academy of Sciences , country =    where lab_id = 2</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>3</v>
       </c>
@@ -5375,11 +5387,11 @@
         <v>22</v>
       </c>
       <c r="N6" t="str">
-        <f>"update lab set lab =  " &amp;C6&amp; " , country =  "&amp;H6&amp;"  where lab_id = "&amp;A6</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Institut des Sciences de la Mer et de l Aménagement du Littoral , country =    where lab_id = 3</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>4</v>
       </c>
@@ -5402,11 +5414,11 @@
         <v>22</v>
       </c>
       <c r="N7" t="str">
-        <f>"update lab set lab =  " &amp;C7&amp; " , country =  "&amp;H7&amp;"  where lab_id = "&amp;A7</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Centre de Radioprotection et Sûreté - Lab. d Environnement , country =    where lab_id = 4</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>5</v>
       </c>
@@ -5426,11 +5438,11 @@
         <v>31</v>
       </c>
       <c r="N8" t="str">
-        <f>"update lab set lab =  " &amp;C8&amp; " , country =  "&amp;H8&amp;"  where lab_id = "&amp;A8</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Central Mining Institute , country =    where lab_id = 5</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>6</v>
       </c>
@@ -5453,11 +5465,11 @@
         <v>37</v>
       </c>
       <c r="N9" t="str">
-        <f>"update lab set lab =  " &amp;C9&amp; " , country =  "&amp;H9&amp;"  where lab_id = "&amp;A9</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Atomic Energy Minerals Centre , country =    where lab_id = 6</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>7</v>
       </c>
@@ -5477,11 +5489,11 @@
         <v>42</v>
       </c>
       <c r="N10" t="str">
-        <f>"update lab set lab =  " &amp;C10&amp; " , country =  "&amp;H10&amp;"  where lab_id = "&amp;A10</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Australian Nuclear Science and Technology Organization - Environmental Services , country =    where lab_id = 7</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>8</v>
       </c>
@@ -5498,11 +5510,11 @@
         <v>42</v>
       </c>
       <c r="N11" t="str">
-        <f>"update lab set lab =  " &amp;C11&amp; " , country =  "&amp;H11&amp;"  where lab_id = "&amp;A11</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Australian Nuclear Science and Technology Organization , country =    where lab_id = 8</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>9</v>
       </c>
@@ -5519,11 +5531,11 @@
         <v>42</v>
       </c>
       <c r="N12" t="str">
-        <f>"update lab set lab =  " &amp;C12&amp; " , country =  "&amp;H12&amp;"  where lab_id = "&amp;A12</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Alligator Rivers Region Research Institute , country =    where lab_id = 9</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>10</v>
       </c>
@@ -5534,11 +5546,11 @@
         <v>48</v>
       </c>
       <c r="N13" t="str">
-        <f>"update lab set lab =  " &amp;C13&amp; " , country =  "&amp;H13&amp;"  where lab_id = "&amp;A13</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  US Coast Guard , country =    where lab_id = 10</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>11</v>
       </c>
@@ -5555,11 +5567,11 @@
         <v>42</v>
       </c>
       <c r="N14" t="str">
-        <f>"update lab set lab =  " &amp;C14&amp; " , country =  "&amp;H14&amp;"  where lab_id = "&amp;A14</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Quality Control Officer - ANALABS , country =    where lab_id = 11</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>12</v>
       </c>
@@ -5576,11 +5588,11 @@
         <v>42</v>
       </c>
       <c r="N15" t="str">
-        <f>"update lab set lab =  " &amp;C15&amp; " , country =  "&amp;H15&amp;"  where lab_id = "&amp;A15</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Office of the Supervising Scientist , country =    where lab_id = 12</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>13</v>
       </c>
@@ -5597,11 +5609,11 @@
         <v>58</v>
       </c>
       <c r="N16" t="str">
-        <f>"update lab set lab =  " &amp;C16&amp; " , country =  "&amp;H16&amp;"  where lab_id = "&amp;A16</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Atominstitut der Osterreichischen Universitäten , country =    where lab_id = 13</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>14</v>
       </c>
@@ -5621,11 +5633,11 @@
         <v>58</v>
       </c>
       <c r="N17" t="str">
-        <f>"update lab set lab =  " &amp;C17&amp; " , country =  "&amp;H17&amp;"  where lab_id = "&amp;A17</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  BALUF Wien , country =    where lab_id = 14</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>15</v>
       </c>
@@ -5642,11 +5654,11 @@
         <v>58</v>
       </c>
       <c r="N18" t="str">
-        <f>"update lab set lab =  " &amp;C18&amp; " , country =  "&amp;H18&amp;"  where lab_id = "&amp;A18</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  BVFA Arsenal - Geotechnisches Institut Isotopengeophysik , country =    where lab_id = 15</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>16</v>
       </c>
@@ -5663,11 +5675,11 @@
         <v>58</v>
       </c>
       <c r="N19" t="str">
-        <f>"update lab set lab =  " &amp;C19&amp; " , country =  "&amp;H19&amp;"  where lab_id = "&amp;A19</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Federal Institute for Food Control and Research - Radiochemistry , country =    where lab_id = 16</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>17</v>
       </c>
@@ -5687,11 +5699,11 @@
         <v>58</v>
       </c>
       <c r="N20" t="str">
-        <f>"update lab set lab =  " &amp;C20&amp; " , country =  "&amp;H20&amp;"  where lab_id = "&amp;A20</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  International Atomic Energy Agency - Seibersdorf Laboratory , country =    where lab_id = 17</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>18</v>
       </c>
@@ -5708,11 +5720,11 @@
         <v>74</v>
       </c>
       <c r="N21" t="str">
-        <f>"update lab set lab =  " &amp;C21&amp; " , country =  "&amp;H21&amp;"  where lab_id = "&amp;A21</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Institute of Physics , country =    where lab_id = 18</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>19</v>
       </c>
@@ -5729,11 +5741,11 @@
         <v>78</v>
       </c>
       <c r="N22" t="str">
-        <f>"update lab set lab =  " &amp;C22&amp; " , country =  "&amp;H22&amp;"  where lab_id = "&amp;A22</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  National Focal Point - Environmental Protection Committee , country =    where lab_id = 19</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>20</v>
       </c>
@@ -5753,11 +5765,11 @@
         <v>83</v>
       </c>
       <c r="N23" t="str">
-        <f>"update lab set lab =  " &amp;C23&amp; " , country =  "&amp;H23&amp;"  where lab_id = "&amp;A23</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Inst. of Nuclear Science &amp; Technology - Atomic Energy Research Establishment , country =    where lab_id = 20</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>21</v>
       </c>
@@ -5774,11 +5786,11 @@
         <v>86</v>
       </c>
       <c r="N24" t="str">
-        <f>"update lab set lab =  " &amp;C24&amp; " , country =  "&amp;H24&amp;"  where lab_id = "&amp;A24</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Laboratoire du C.E.N -  S.C.K - Section de Spectrométrie Nucléaire , country =    where lab_id = 21</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>22</v>
       </c>
@@ -5792,11 +5804,11 @@
         <v>48</v>
       </c>
       <c r="N25" t="str">
-        <f>"update lab set lab =  " &amp;C25&amp; " , country =  "&amp;H25&amp;"  where lab_id = "&amp;A25</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Lamont Doherty Geological Observatory , country =    where lab_id = 22</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>23</v>
       </c>
@@ -5816,11 +5828,11 @@
         <v>93</v>
       </c>
       <c r="N26" t="str">
-        <f>"update lab set lab =  " &amp;C26&amp; " , country =  "&amp;H26&amp;"  where lab_id = "&amp;A26</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Universidad Mayor de San Andrés - Facultad de Ciencias Puras y Naturales , country =    where lab_id = 23</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>24</v>
       </c>
@@ -5840,11 +5852,11 @@
         <v>93</v>
       </c>
       <c r="N27" t="str">
-        <f>"update lab set lab =  " &amp;C27&amp; " , country =  "&amp;H27&amp;"  where lab_id = "&amp;A27</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Instituto Boliviano de Ciencias y Tecnologia Nuclear - PNUD , country =    where lab_id = 24</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>25</v>
       </c>
@@ -5858,11 +5870,11 @@
         <v>99</v>
       </c>
       <c r="N28" t="str">
-        <f>"update lab set lab =  " &amp;C28&amp; " , country =  "&amp;H28&amp;"  where lab_id = "&amp;A28</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  National Swedish Environmental Protection, Coastal Research Lab , country =    where lab_id = 25</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>26</v>
       </c>
@@ -5876,11 +5888,11 @@
         <v>102</v>
       </c>
       <c r="N29" t="str">
-        <f>"update lab set lab =  " &amp;C29&amp; " , country =  "&amp;H29&amp;"  where lab_id = "&amp;A29</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Veterinary Faculty of the University of Sarajevo , country =    where lab_id = 26</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>27</v>
       </c>
@@ -5894,11 +5906,11 @@
         <v>105</v>
       </c>
       <c r="N30" t="str">
-        <f>"update lab set lab =  " &amp;C30&amp; " , country =  "&amp;H30&amp;"  where lab_id = "&amp;A30</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Inst for Experimental Meteorology , country =    where lab_id = 27</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>28</v>
       </c>
@@ -5918,11 +5930,11 @@
         <v>109</v>
       </c>
       <c r="N31" t="str">
-        <f>"update lab set lab =  " &amp;C31&amp; " , country =  "&amp;H31&amp;"  where lab_id = "&amp;A31</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Instituto de Pesquisas Energéticas e Nucleares , country =    where lab_id = 28</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>29</v>
       </c>
@@ -5942,11 +5954,11 @@
         <v>109</v>
       </c>
       <c r="N32" t="str">
-        <f>"update lab set lab =  " &amp;C32&amp; " , country =  "&amp;H32&amp;"  where lab_id = "&amp;A32</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Furnas Centrais Eletricas S.A. - CNAAA - Laboratorio de Radioecolog. , country =    where lab_id = 29</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>30</v>
       </c>
@@ -5966,11 +5978,11 @@
         <v>109</v>
       </c>
       <c r="N33" t="str">
-        <f>"update lab set lab =  " &amp;C33&amp; " , country =  "&amp;H33&amp;"  where lab_id = "&amp;A33</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Furnas Centrais Eletricas S.A. - Depart. de Geracao de Angra. , country =    where lab_id = 30</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>31</v>
       </c>
@@ -5990,11 +6002,11 @@
         <v>109</v>
       </c>
       <c r="N34" t="str">
-        <f>"update lab set lab =  " &amp;C34&amp; " , country =  "&amp;H34&amp;"  where lab_id = "&amp;A34</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Instituto de Pesquisas Energéticas e Nucleares - Environmental Monitoring Division  , country =    where lab_id = 31</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>32</v>
       </c>
@@ -6008,11 +6020,11 @@
         <v>109</v>
       </c>
       <c r="N35" t="str">
-        <f>"update lab set lab =  " &amp;C35&amp; " , country =  "&amp;H35&amp;"  where lab_id = "&amp;A35</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Instituto de Radioprotecao e Dosimetria , country =    where lab_id = 32</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>33</v>
       </c>
@@ -6029,11 +6041,11 @@
         <v>125</v>
       </c>
       <c r="N36" t="str">
-        <f>"update lab set lab =  " &amp;C36&amp; " , country =  "&amp;H36&amp;"  where lab_id = "&amp;A36</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Institute of Nuclear Medicine Radiobiology &amp; Radiation Hygiene - Radiation Hygiene Research Division , country =    where lab_id = 33</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>34</v>
       </c>
@@ -6047,11 +6059,11 @@
         <v>128</v>
       </c>
       <c r="N37" t="str">
-        <f>"update lab set lab =  " &amp;C37&amp; " , country =  "&amp;H37&amp;"  where lab_id = "&amp;A37</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Atomic Energy of Canada Ltd. - Whiteshell Nuclear Research Establ. , country =    where lab_id = 34</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>35</v>
       </c>
@@ -6071,11 +6083,11 @@
         <v>128</v>
       </c>
       <c r="N38" t="str">
-        <f>"update lab set lab =  " &amp;C38&amp; " , country =  "&amp;H38&amp;"  where lab_id = "&amp;A38</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Senior Research Officer and Visiting Professor , country =    where lab_id = 35</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>36</v>
       </c>
@@ -6095,11 +6107,11 @@
         <v>128</v>
       </c>
       <c r="N39" t="str">
-        <f>"update lab set lab =  " &amp;C39&amp; " , country =  "&amp;H39&amp;"  where lab_id = "&amp;A39</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Environmental Radiation Hazards D. - Bureau of Radiation &amp; Med. Devices , country =    where lab_id = 36</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>37</v>
       </c>
@@ -6122,11 +6134,11 @@
         <v>128</v>
       </c>
       <c r="N40" t="str">
-        <f>"update lab set lab =  " &amp;C40&amp; " , country =  "&amp;H40&amp;"  where lab_id = "&amp;A40</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Bedford Institute of Oceanography - Dept. of Fisheries and Oceans , country =    where lab_id = 37</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>38</v>
       </c>
@@ -6146,11 +6158,11 @@
         <v>128</v>
       </c>
       <c r="N41" t="str">
-        <f>"update lab set lab =  " &amp;C41&amp; " , country =  "&amp;H41&amp;"  where lab_id = "&amp;A41</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Atlantic Environ. Radiation Unit - Bedford Institute of Oceanography , country =    where lab_id = 38</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>39</v>
       </c>
@@ -6167,11 +6179,11 @@
         <v>128</v>
       </c>
       <c r="N42" t="str">
-        <f>"update lab set lab =  " &amp;C42&amp; " , country =  "&amp;H42&amp;"  where lab_id = "&amp;A42</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Ontario Ministry of Labour - Radiation Protection Service , country =    where lab_id = 39</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>40</v>
       </c>
@@ -6188,11 +6200,11 @@
         <v>128</v>
       </c>
       <c r="N43" t="str">
-        <f>"update lab set lab =  " &amp;C43&amp; " , country =  "&amp;H43&amp;"  where lab_id = "&amp;A43</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Fisheries and Oceans Canada - Freshwater Institute , country =    where lab_id = 40</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>41</v>
       </c>
@@ -6209,11 +6221,11 @@
         <v>128</v>
       </c>
       <c r="N44" t="str">
-        <f>"update lab set lab =  " &amp;C44&amp; " , country =  "&amp;H44&amp;"  where lab_id = "&amp;A44</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Ecole Polytechnique , country =    where lab_id = 41</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>42</v>
       </c>
@@ -6233,11 +6245,11 @@
         <v>155</v>
       </c>
       <c r="N45" t="str">
-        <f>"update lab set lab =  " &amp;C45&amp; " , country =  "&amp;H45&amp;"  where lab_id = "&amp;A45</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Direccion General del Territorio Maritimo y de Marina Mercante , country =    where lab_id = 42</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>43</v>
       </c>
@@ -6251,11 +6263,11 @@
         <v>158</v>
       </c>
       <c r="N46" t="str">
-        <f>"update lab set lab =  " &amp;C46&amp; " , country =  "&amp;H46&amp;"  where lab_id = "&amp;A46</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Third Institute of Oceanography - State Oceanic Administration , country =    where lab_id = 43</v>
       </c>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>44</v>
       </c>
@@ -6269,11 +6281,11 @@
         <v>128</v>
       </c>
       <c r="N47" t="str">
-        <f>"update lab set lab =  " &amp;C47&amp; " , country =  "&amp;H47&amp;"  where lab_id = "&amp;A47</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  McMasters University , country =    where lab_id = 44</v>
       </c>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>45</v>
       </c>
@@ -6293,11 +6305,11 @@
         <v>158</v>
       </c>
       <c r="N48" t="str">
-        <f>"update lab set lab =  " &amp;C48&amp; " , country =  "&amp;H48&amp;"  where lab_id = "&amp;A48</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Institute of Radiation Medicine - Chinese Academy of Medical Sciences , country =    where lab_id = 45</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>46</v>
       </c>
@@ -6311,11 +6323,11 @@
         <v>158</v>
       </c>
       <c r="N49" t="str">
-        <f>"update lab set lab =  " &amp;C49&amp; " , country =  "&amp;H49&amp;"  where lab_id = "&amp;A49</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Nanjing University - Department of GEO &amp; OCEAN Services , country =    where lab_id = 46</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>47</v>
       </c>
@@ -6335,11 +6347,11 @@
         <v>158</v>
       </c>
       <c r="N50" t="str">
-        <f>"update lab set lab =  " &amp;C50&amp; " , country =  "&amp;H50&amp;"  where lab_id = "&amp;A50</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  First Institute of Oceanography , country =    where lab_id = 47</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>48</v>
       </c>
@@ -6356,11 +6368,11 @@
         <v>158</v>
       </c>
       <c r="N51" t="str">
-        <f>"update lab set lab =  " &amp;C51&amp; " , country =  "&amp;H51&amp;"  where lab_id = "&amp;A51</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Beijing Institute of Chemical Engineering and Metallurgy , country =    where lab_id = 48</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>49</v>
       </c>
@@ -6377,11 +6389,11 @@
         <v>177</v>
       </c>
       <c r="N52" t="str">
-        <f>"update lab set lab =  " &amp;C52&amp; " , country =  "&amp;H52&amp;"  where lab_id = "&amp;A52</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  AEA Technology - Winfrith Technology Centre , country =    where lab_id = 49</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>50</v>
       </c>
@@ -6398,11 +6410,11 @@
         <v>158</v>
       </c>
       <c r="N53" t="str">
-        <f>"update lab set lab =  " &amp;C53&amp; " , country =  "&amp;H53&amp;"  where lab_id = "&amp;A53</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  China Institute for Radiation Protection , country =    where lab_id = 50</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>51</v>
       </c>
@@ -6419,11 +6431,11 @@
         <v>158</v>
       </c>
       <c r="N54" t="str">
-        <f>"update lab set lab =  " &amp;C54&amp; " , country =  "&amp;H54&amp;"  where lab_id = "&amp;A54</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  China Institute of Atomic Energy , country =    where lab_id = 51</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>52</v>
       </c>
@@ -6440,11 +6452,11 @@
         <v>187</v>
       </c>
       <c r="N55" t="str">
-        <f>"update lab set lab =  " &amp;C55&amp; " , country =  "&amp;H55&amp;"  where lab_id = "&amp;A55</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Institute of Oceanography and Fisheries , country =    where lab_id = 52</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>53</v>
       </c>
@@ -6464,11 +6476,11 @@
         <v>187</v>
       </c>
       <c r="N56" t="str">
-        <f>"update lab set lab =  " &amp;C56&amp; " , country =  "&amp;H56&amp;"  where lab_id = "&amp;A56</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Inst. for Med. Res. &amp; Occ. Health - Department of Radiation Protection , country =    where lab_id = 53</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>54</v>
       </c>
@@ -6485,11 +6497,11 @@
         <v>187</v>
       </c>
       <c r="N57" t="str">
-        <f>"update lab set lab =  " &amp;C57&amp; " , country =  "&amp;H57&amp;"  where lab_id = "&amp;A57</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Institute of Public Health , country =    where lab_id = 54</v>
       </c>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>55</v>
       </c>
@@ -6506,11 +6518,11 @@
         <v>197</v>
       </c>
       <c r="N58" t="str">
-        <f>"update lab set lab =  " &amp;C58&amp; " , country =  "&amp;H58&amp;"  where lab_id = "&amp;A58</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Higher Environmental Committee - Ministry of Health , country =    where lab_id = 55</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>56</v>
       </c>
@@ -6527,11 +6539,11 @@
         <v>187</v>
       </c>
       <c r="N59" t="str">
-        <f>"update lab set lab =  " &amp;C59&amp; " , country =  "&amp;H59&amp;"  where lab_id = "&amp;A59</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =   Ruder Boskovic  Institute Centre for Marine Research , country =    where lab_id = 56</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>57</v>
       </c>
@@ -6548,11 +6560,11 @@
         <v>203</v>
       </c>
       <c r="N60" t="str">
-        <f>"update lab set lab =  " &amp;C60&amp; " , country =  "&amp;H60&amp;"  where lab_id = "&amp;A60</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Ellauri 533 , country =    where lab_id = 57</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>58</v>
       </c>
@@ -6572,11 +6584,11 @@
         <v>203</v>
       </c>
       <c r="N61" t="str">
-        <f>"update lab set lab =  " &amp;C61&amp; " , country =  "&amp;H61&amp;"  where lab_id = "&amp;A61</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Chemical Engineer - S.O.H.M.A. , country =    where lab_id = 58</v>
       </c>
     </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>59</v>
       </c>
@@ -6596,11 +6608,11 @@
         <v>187</v>
       </c>
       <c r="N62" t="str">
-        <f>"update lab set lab =  " &amp;C62&amp; " , country =  "&amp;H62&amp;"  where lab_id = "&amp;A62</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =   Ruder Boskovic  Institute - Centre for Marine Research Zagreb , country =    where lab_id = 59</v>
       </c>
     </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>60</v>
       </c>
@@ -6617,11 +6629,11 @@
         <v>213</v>
       </c>
       <c r="N63" t="str">
-        <f>"update lab set lab =  " &amp;C63&amp; " , country =  "&amp;H63&amp;"  where lab_id = "&amp;A63</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Institute of Nuclear Research - Academia de Ciencias de Cuba , country =    where lab_id = 60</v>
       </c>
     </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>61</v>
       </c>
@@ -6638,11 +6650,11 @@
         <v>203</v>
       </c>
       <c r="N64" t="str">
-        <f>"update lab set lab =  " &amp;C64&amp; " , country =  "&amp;H64&amp;"  where lab_id = "&amp;A64</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Catedra de Radioquimica - Facultad de Quimica , country =    where lab_id = 61</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>62</v>
       </c>
@@ -6662,11 +6674,11 @@
         <v>213</v>
       </c>
       <c r="N65" t="str">
-        <f>"update lab set lab =  " &amp;C65&amp; " , country =  "&amp;H65&amp;"  where lab_id = "&amp;A65</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Centro de Proteccion e Hygiene de las Radiaciones , country =    where lab_id = 62</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>63</v>
       </c>
@@ -6686,11 +6698,11 @@
         <v>224</v>
       </c>
       <c r="N66" t="str">
-        <f>"update lab set lab =  " &amp;C66&amp; " , country =  "&amp;H66&amp;"  where lab_id = "&amp;A66</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  Ministry of Agriculture and Natural Resources , country =    where lab_id = 63</v>
       </c>
     </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>64</v>
       </c>
@@ -6707,11 +6719,11 @@
         <v>228</v>
       </c>
       <c r="N67" t="str">
-        <f>"update lab set lab =  " &amp;C67&amp; " , country =  "&amp;H67&amp;"  where lab_id = "&amp;A67</f>
+        <f t="shared" si="0"/>
         <v>update lab set lab =  MEGA -  a.s. , country =    where lab_id = 64</v>
       </c>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>65</v>
       </c>
@@ -6728,11 +6740,11 @@
         <v>228</v>
       </c>
       <c r="N68" t="str">
-        <f>"update lab set lab =  " &amp;C68&amp; " , country =  "&amp;H68&amp;"  where lab_id = "&amp;A68</f>
+        <f t="shared" ref="N68:N131" si="1">"update lab set lab =  " &amp;C68&amp; " , country =  "&amp;H68&amp;"  where lab_id = "&amp;A68</f>
         <v>update lab set lab =  Institute of Radioecology and Applied Nuclear Techniques , country =    where lab_id = 65</v>
       </c>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>66</v>
       </c>
@@ -6752,11 +6764,11 @@
         <v>228</v>
       </c>
       <c r="N69" t="str">
-        <f>"update lab set lab =  " &amp;C69&amp; " , country =  "&amp;H69&amp;"  where lab_id = "&amp;A69</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Laboratory of Spectrometry Centre of Radiation Hygiene , country =    where lab_id = 66</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>67</v>
       </c>
@@ -6773,11 +6785,11 @@
         <v>228</v>
       </c>
       <c r="N70" t="str">
-        <f>"update lab set lab =  " &amp;C70&amp; " , country =  "&amp;H70&amp;"  where lab_id = "&amp;A70</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Research Institute of Preventive Medicine , country =    where lab_id = 67</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>68</v>
       </c>
@@ -6794,11 +6806,11 @@
         <v>125</v>
       </c>
       <c r="N71" t="str">
-        <f>"update lab set lab =  " &amp;C71&amp; " , country =  "&amp;H71&amp;"  where lab_id = "&amp;A71</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Geological Survey , country =    where lab_id = 68</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>69</v>
       </c>
@@ -6818,11 +6830,11 @@
         <v>228</v>
       </c>
       <c r="N72" t="str">
-        <f>"update lab set lab =  " &amp;C72&amp; " , country =  "&amp;H72&amp;"  where lab_id = "&amp;A72</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  V U J E - Nuclear Power Plants , country =    where lab_id = 69</v>
       </c>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>70</v>
       </c>
@@ -6839,11 +6851,11 @@
         <v>48</v>
       </c>
       <c r="N73" t="str">
-        <f>"update lab set lab =  " &amp;C73&amp; " , country =  "&amp;H73&amp;"  where lab_id = "&amp;A73</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Harvard University - Harvard University Center for the Environment , country =    where lab_id = 70</v>
       </c>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>71</v>
       </c>
@@ -6863,11 +6875,11 @@
         <v>253</v>
       </c>
       <c r="N74" t="str">
-        <f>"update lab set lab =  " &amp;C74&amp; " , country =  "&amp;H74&amp;"  where lab_id = "&amp;A74</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Comision Ecuatoriana de Energia Atomica , country =    where lab_id = 71</v>
       </c>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>72</v>
       </c>
@@ -6887,11 +6899,11 @@
         <v>257</v>
       </c>
       <c r="N75" t="str">
-        <f>"update lab set lab =  " &amp;C75&amp; " , country =  "&amp;H75&amp;"  where lab_id = "&amp;A75</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Institute of Oceanography and Fisheries , country =    where lab_id = 72</v>
       </c>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>73</v>
       </c>
@@ -6911,11 +6923,11 @@
         <v>257</v>
       </c>
       <c r="N76" t="str">
-        <f>"update lab set lab =  " &amp;C76&amp; " , country =  "&amp;H76&amp;"  where lab_id = "&amp;A76</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Institute of Graduate Studies and Research , country =    where lab_id = 73</v>
       </c>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>74</v>
       </c>
@@ -6935,11 +6947,11 @@
         <v>257</v>
       </c>
       <c r="N77" t="str">
-        <f>"update lab set lab =  " &amp;C77&amp; " , country =  "&amp;H77&amp;"  where lab_id = "&amp;A77</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Nuclear Power Plants Authority , country =    where lab_id = 74</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>75</v>
       </c>
@@ -6956,11 +6968,11 @@
         <v>268</v>
       </c>
       <c r="N78" t="str">
-        <f>"update lab set lab =  " &amp;C78&amp; " , country =  "&amp;H78&amp;"  where lab_id = "&amp;A78</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Institute of Biology of South Seas - Academy of Sciences of Ukraine , country =    where lab_id = 75</v>
       </c>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>76</v>
       </c>
@@ -6980,11 +6992,11 @@
         <v>257</v>
       </c>
       <c r="N79" t="str">
-        <f>"update lab set lab =  " &amp;C79&amp; " , country =  "&amp;H79&amp;"  where lab_id = "&amp;A79</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Environmental and Occupational Health Centre , country =    where lab_id = 76</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>77</v>
       </c>
@@ -7007,11 +7019,11 @@
         <v>277</v>
       </c>
       <c r="N80" t="str">
-        <f>"update lab set lab =  " &amp;C80&amp; " , country =  "&amp;H80&amp;"  where lab_id = "&amp;A80</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Finnish Centre for Radiation and Nuclear Safety , country =    where lab_id = 77</v>
       </c>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>78</v>
       </c>
@@ -7031,11 +7043,11 @@
         <v>282</v>
       </c>
       <c r="N81" t="str">
-        <f>"update lab set lab =  " &amp;C81&amp; " , country =  "&amp;H81&amp;"  where lab_id = "&amp;A81</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Laboratoire de Radiochimie - Faculté des Sciences , country =    where lab_id = 78</v>
       </c>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>79</v>
       </c>
@@ -7052,11 +7064,11 @@
         <v>268</v>
       </c>
       <c r="N82" t="str">
-        <f>"update lab set lab =  " &amp;C82&amp; " , country =  "&amp;H82&amp;"  where lab_id = "&amp;A82</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Marine Hydrophysical Institute - Academy of Sciences of Ukraine , country =    where lab_id = 79</v>
       </c>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>80</v>
       </c>
@@ -7079,11 +7091,11 @@
         <v>282</v>
       </c>
       <c r="N83" t="str">
-        <f>"update lab set lab =  " &amp;C83&amp; " , country =  "&amp;H83&amp;"  where lab_id = "&amp;A83</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Commissariat à l énergie atomique et aux énergies alternatives , country =    where lab_id = 80</v>
       </c>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>81</v>
       </c>
@@ -7106,11 +7118,11 @@
         <v>48</v>
       </c>
       <c r="N84" t="str">
-        <f>"update lab set lab =  " &amp;C84&amp; " , country =  "&amp;H84&amp;"  where lab_id = "&amp;A84</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Lawrence Livermore National Laboratory , country =    where lab_id = 81</v>
       </c>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>82</v>
       </c>
@@ -7130,11 +7142,11 @@
         <v>282</v>
       </c>
       <c r="N85" t="str">
-        <f>"update lab set lab =  " &amp;C85&amp; " , country =  "&amp;H85&amp;"  where lab_id = "&amp;A85</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  COGEMA - Groupe Environnement , country =    where lab_id = 82</v>
       </c>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>83</v>
       </c>
@@ -7154,11 +7166,11 @@
         <v>282</v>
       </c>
       <c r="N86" t="str">
-        <f>"update lab set lab =  " &amp;C86&amp; " , country =  "&amp;H86&amp;"  where lab_id = "&amp;A86</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Commissariat à l énergie atomique et aux énergies alternatives - Direction Centrale - SMSR , country =    where lab_id = 83</v>
       </c>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>84</v>
       </c>
@@ -7178,11 +7190,11 @@
         <v>282</v>
       </c>
       <c r="N87" t="str">
-        <f>"update lab set lab =  " &amp;C87&amp; " , country =  "&amp;H87&amp;"  where lab_id = "&amp;A87</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Centre de Recherches du Service de Santé des Armées , country =    where lab_id = 84</v>
       </c>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>85</v>
       </c>
@@ -7202,11 +7214,11 @@
         <v>282</v>
       </c>
       <c r="N88" t="str">
-        <f>"update lab set lab =  " &amp;C88&amp; " , country =  "&amp;H88&amp;"  where lab_id = "&amp;A88</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  I.P.S.N. - DPEI -  SERE _LMEI_ , country =    where lab_id = 85</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>86</v>
       </c>
@@ -7226,11 +7238,11 @@
         <v>282</v>
       </c>
       <c r="N89" t="str">
-        <f>"update lab set lab =  " &amp;C89&amp; " , country =  "&amp;H89&amp;"  where lab_id = "&amp;A89</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  IFREMER - Centre de Toulon _CEA - S.M.T._ , country =    where lab_id = 86</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>87</v>
       </c>
@@ -7250,11 +7262,11 @@
         <v>282</v>
       </c>
       <c r="N90" t="str">
-        <f>"update lab set lab =  " &amp;C90&amp; " , country =  "&amp;H90&amp;"  where lab_id = "&amp;A90</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Laboratoire de Radioécologie des Eaux Continentales , country =    where lab_id = 87</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>88</v>
       </c>
@@ -7268,11 +7280,11 @@
         <v>282</v>
       </c>
       <c r="N91" t="str">
-        <f>"update lab set lab =  " &amp;C91&amp; " , country =  "&amp;H91&amp;"  where lab_id = "&amp;A91</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Institut de Protection et de Sûreté Nucléaire - DPEI , country =    where lab_id = 88</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>89</v>
       </c>
@@ -7289,11 +7301,11 @@
         <v>282</v>
       </c>
       <c r="N92" t="str">
-        <f>"update lab set lab =  " &amp;C92&amp; " , country =  "&amp;H92&amp;"  where lab_id = "&amp;A92</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Marine Nationale Section de Surveillance Radiologique , country =    where lab_id = 89</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>90</v>
       </c>
@@ -7307,11 +7319,11 @@
         <v>282</v>
       </c>
       <c r="N93" t="str">
-        <f>"update lab set lab =  " &amp;C93&amp; " , country =  "&amp;H93&amp;"  where lab_id = "&amp;A93</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Centre des Faibles Radioactivités - Laboratoire Mixte CNRS-CEA , country =    where lab_id = 90</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>91</v>
       </c>
@@ -7331,11 +7343,11 @@
         <v>282</v>
       </c>
       <c r="N94" t="str">
-        <f>"update lab set lab =  " &amp;C94&amp; " , country =  "&amp;H94&amp;"  where lab_id = "&amp;A94</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Service de Sécurité Radiologique du port de Brest , country =    where lab_id = 91</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>92</v>
       </c>
@@ -7352,11 +7364,11 @@
         <v>282</v>
       </c>
       <c r="N95" t="str">
-        <f>"update lab set lab =  " &amp;C95&amp; " , country =  "&amp;H95&amp;"  where lab_id = "&amp;A95</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Institut de Biogéochimie Marine - Ecole Normale Supérieure  _ENS_ , country =    where lab_id = 92</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>93</v>
       </c>
@@ -7376,11 +7388,11 @@
         <v>332</v>
       </c>
       <c r="N96" t="str">
-        <f>"update lab set lab =  " &amp;C96&amp; " , country =  "&amp;H96&amp;"  where lab_id = "&amp;A96</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Universidad Simon Bolivar - Laboratorio de Fisica Nuclear , country =    where lab_id = 93</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>94</v>
       </c>
@@ -7400,11 +7412,11 @@
         <v>335</v>
       </c>
       <c r="N97" t="str">
-        <f>"update lab set lab =  " &amp;C97&amp; " , country =  "&amp;H97&amp;"  where lab_id = "&amp;A97</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Institut de Protection et de Sûreté Nucléaire - Lab. d Etude et de Surveillance de l Environnement , country =    where lab_id = 94</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>95</v>
       </c>
@@ -7424,11 +7436,11 @@
         <v>340</v>
       </c>
       <c r="N98" t="str">
-        <f>"update lab set lab =  " &amp;C98&amp; " , country =  "&amp;H98&amp;"  where lab_id = "&amp;A98</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Kernforschungszentrum Karlsruhe Hauptabteilung Sicherheit , country =    where lab_id = 95</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>96</v>
       </c>
@@ -7445,11 +7457,11 @@
         <v>340</v>
       </c>
       <c r="N99" t="str">
-        <f>"update lab set lab =  " &amp;C99&amp; " , country =  "&amp;H99&amp;"  where lab_id = "&amp;A99</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Institut für Wässer Boden und Lufthygiene des Bundesgesund. , country =    where lab_id = 96</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>97</v>
       </c>
@@ -7469,11 +7481,11 @@
         <v>340</v>
       </c>
       <c r="N100" t="str">
-        <f>"update lab set lab =  " &amp;C100&amp; " , country =  "&amp;H100&amp;"  where lab_id = "&amp;A100</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Landesuntersuchungsamt für das Gesundheitswesen Nordbayern , country =    where lab_id = 97</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>98</v>
       </c>
@@ -7490,11 +7502,11 @@
         <v>340</v>
       </c>
       <c r="N101" t="str">
-        <f>"update lab set lab =  " &amp;C101&amp; " , country =  "&amp;H101&amp;"  where lab_id = "&amp;A101</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Ingenieurgesellschaft IAF , country =    where lab_id = 98</v>
       </c>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>99</v>
       </c>
@@ -7511,11 +7523,11 @@
         <v>340</v>
       </c>
       <c r="N102" t="str">
-        <f>"update lab set lab =  " &amp;C102&amp; " , country =  "&amp;H102&amp;"  where lab_id = "&amp;A102</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Institut für Wabohu-Hygiene _Labor BI 2_ , country =    where lab_id = 99</v>
       </c>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>100</v>
       </c>
@@ -7535,11 +7547,11 @@
         <v>332</v>
       </c>
       <c r="N103" t="str">
-        <f>"update lab set lab =  " &amp;C103&amp; " , country =  "&amp;H103&amp;"  where lab_id = "&amp;A103</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Laboratorio de Espectroscopia Atomica y Nuclear , country =    where lab_id = 100</v>
       </c>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>101</v>
       </c>
@@ -7559,11 +7571,11 @@
         <v>340</v>
       </c>
       <c r="N104" t="str">
-        <f>"update lab set lab =  " &amp;C104&amp; " , country =  "&amp;H104&amp;"  where lab_id = "&amp;A104</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Sektion Physik - WB Angewandte Physik , country =    where lab_id = 101</v>
       </c>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>102</v>
       </c>
@@ -7583,11 +7595,11 @@
         <v>332</v>
       </c>
       <c r="N105" t="str">
-        <f>"update lab set lab =  " &amp;C105&amp; " , country =  "&amp;H105&amp;"  where lab_id = "&amp;A105</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  IVIC - Lab. de Mineralogia , country =    where lab_id = 102</v>
       </c>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>103</v>
       </c>
@@ -7607,11 +7619,11 @@
         <v>340</v>
       </c>
       <c r="N106" t="str">
-        <f>"update lab set lab =  " &amp;C106&amp; " , country =  "&amp;H106&amp;"  where lab_id = "&amp;A106</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Verein für Kernverfahrenstechnik und Analytik Rossendorf e.V. , country =    where lab_id = 103</v>
       </c>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>104</v>
       </c>
@@ -7631,11 +7643,11 @@
         <v>340</v>
       </c>
       <c r="N107" t="str">
-        <f>"update lab set lab =  " &amp;C107&amp; " , country =  "&amp;H107&amp;"  where lab_id = "&amp;A107</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  GKSS - Forschungszentrum Geesthacht , country =    where lab_id = 104</v>
       </c>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>105</v>
       </c>
@@ -7658,11 +7670,11 @@
         <v>340</v>
       </c>
       <c r="N108" t="str">
-        <f>"update lab set lab =  " &amp;C108&amp; " , country =  "&amp;H108&amp;"  where lab_id = "&amp;A108</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Bundesforschungsanstalt für fisher. , country =    where lab_id = 105</v>
       </c>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>106</v>
       </c>
@@ -7682,11 +7694,11 @@
         <v>340</v>
       </c>
       <c r="N109" t="str">
-        <f>"update lab set lab =  " &amp;C109&amp; " , country =  "&amp;H109&amp;"  where lab_id = "&amp;A109</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Hessische , country =    where lab_id = 106</v>
       </c>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>107</v>
       </c>
@@ -7703,11 +7715,11 @@
         <v>340</v>
       </c>
       <c r="N110" t="str">
-        <f>"update lab set lab =  " &amp;C110&amp; " , country =  "&amp;H110&amp;"  where lab_id = "&amp;A110</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Strahlenbiologisches Institut der Universität München , country =    where lab_id = 107</v>
       </c>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>108</v>
       </c>
@@ -7724,11 +7736,11 @@
         <v>340</v>
       </c>
       <c r="N111" t="str">
-        <f>"update lab set lab =  " &amp;C111&amp; " , country =  "&amp;H111&amp;"  where lab_id = "&amp;A111</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Staatliches amt für Atomsicherheit und Strahlenschutz , country =    where lab_id = 108</v>
       </c>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>109</v>
       </c>
@@ -7748,11 +7760,11 @@
         <v>340</v>
       </c>
       <c r="N112" t="str">
-        <f>"update lab set lab =  " &amp;C112&amp; " , country =  "&amp;H112&amp;"  where lab_id = "&amp;A112</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Fachbereich Physikalische Chemie der Philipps - Universitaet , country =    where lab_id = 109</v>
       </c>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>110</v>
       </c>
@@ -7772,11 +7784,11 @@
         <v>340</v>
       </c>
       <c r="N113" t="str">
-        <f>"update lab set lab =  " &amp;C113&amp; " , country =  "&amp;H113&amp;"  where lab_id = "&amp;A113</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Federal Maritime and Hydrographic Agency , country =    where lab_id = 110</v>
       </c>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>111</v>
       </c>
@@ -7793,11 +7805,11 @@
         <v>340</v>
       </c>
       <c r="N114" t="str">
-        <f>"update lab set lab =  " &amp;C114&amp; " , country =  "&amp;H114&amp;"  where lab_id = "&amp;A114</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Zentralinstitut für Kernforschung Rossendorf , country =    where lab_id = 111</v>
       </c>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>112</v>
       </c>
@@ -7814,11 +7826,11 @@
         <v>400</v>
       </c>
       <c r="N115" t="str">
-        <f>"update lab set lab =  " &amp;C115&amp; " , country =  "&amp;H115&amp;"  where lab_id = "&amp;A115</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Nuclear Research Institute , country =    where lab_id = 112</v>
       </c>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>113</v>
       </c>
@@ -7832,11 +7844,11 @@
         <v>340</v>
       </c>
       <c r="N116" t="str">
-        <f>"update lab set lab =  " &amp;C116&amp; " , country =  "&amp;H116&amp;"  where lab_id = "&amp;A116</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Institute of Applied Physical Chem. - Nuclear Research Centre - Jülich , country =    where lab_id = 113</v>
       </c>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>114</v>
       </c>
@@ -7856,11 +7868,11 @@
         <v>340</v>
       </c>
       <c r="N117" t="str">
-        <f>"update lab set lab =  " &amp;C117&amp; " , country =  "&amp;H117&amp;"  where lab_id = "&amp;A117</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Akademie der Wissenschaften - Zentralinstitut für Kernforschung , country =    where lab_id = 114</v>
       </c>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>115</v>
       </c>
@@ -7877,11 +7889,11 @@
         <v>340</v>
       </c>
       <c r="N118" t="str">
-        <f>"update lab set lab =  " &amp;C118&amp; " , country =  "&amp;H118&amp;"  where lab_id = "&amp;A118</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Kernforschungszentrum Karlsruhe _BFE  BAU 325_ , country =    where lab_id = 115</v>
       </c>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>116</v>
       </c>
@@ -7898,11 +7910,11 @@
         <v>400</v>
       </c>
       <c r="N119" t="str">
-        <f>"update lab set lab =  " &amp;C119&amp; " , country =  "&amp;H119&amp;"  where lab_id = "&amp;A119</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Vietnam National Atomic Energy Commission , country =    where lab_id = 116</v>
       </c>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>117</v>
       </c>
@@ -7919,11 +7931,11 @@
         <v>340</v>
       </c>
       <c r="N120" t="str">
-        <f>"update lab set lab =  " &amp;C120&amp; " , country =  "&amp;H120&amp;"  where lab_id = "&amp;A120</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Niedersaechsisches Landesamt für Wasser und Abfall , country =    where lab_id = 117</v>
       </c>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>118</v>
       </c>
@@ -7940,11 +7952,11 @@
         <v>340</v>
       </c>
       <c r="N121" t="str">
-        <f>"update lab set lab =  " &amp;C121&amp; " , country =  "&amp;H121&amp;"  where lab_id = "&amp;A121</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  National Board of Nuclear Safety and Radiation Protection , country =    where lab_id = 118</v>
       </c>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>119</v>
       </c>
@@ -7961,11 +7973,11 @@
         <v>340</v>
       </c>
       <c r="N122" t="str">
-        <f>"update lab set lab =  " &amp;C122&amp; " , country =  "&amp;H122&amp;"  where lab_id = "&amp;A122</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Bergakademie Freiberg - Sektion Physik , country =    where lab_id = 119</v>
       </c>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>120</v>
       </c>
@@ -7985,11 +7997,11 @@
         <v>340</v>
       </c>
       <c r="N123" t="str">
-        <f>"update lab set lab =  " &amp;C123&amp; " , country =  "&amp;H123&amp;"  where lab_id = "&amp;A123</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Physikalisch-Technische Bundesanst. , country =    where lab_id = 120</v>
       </c>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>121</v>
       </c>
@@ -8006,11 +8018,11 @@
         <v>421</v>
       </c>
       <c r="N124" t="str">
-        <f>"update lab set lab =  " &amp;C124&amp; " , country =  "&amp;H124&amp;"  where lab_id = "&amp;A124</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Dept. of Physics -  Reactor Technology - Ghana Atomic Energy Commission , country =    where lab_id = 121</v>
       </c>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>122</v>
       </c>
@@ -8030,11 +8042,11 @@
         <v>425</v>
       </c>
       <c r="N125" t="str">
-        <f>"update lab set lab =  " &amp;C125&amp; " , country =  "&amp;H125&amp;"  where lab_id = "&amp;A125</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  NCSR  Demokritos  - Institute of Nuclear Technology , country =    where lab_id = 122</v>
       </c>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>123</v>
       </c>
@@ -8051,11 +8063,11 @@
         <v>429</v>
       </c>
       <c r="N126" t="str">
-        <f>"update lab set lab =  " &amp;C126&amp; " , country =  "&amp;H126&amp;"  where lab_id = "&amp;A126</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Royal Observatory - Hong Kong Government , country =    where lab_id = 123</v>
       </c>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>124</v>
       </c>
@@ -8072,11 +8084,11 @@
         <v>433</v>
       </c>
       <c r="N127" t="str">
-        <f>"update lab set lab =  " &amp;C127&amp; " , country =  "&amp;H127&amp;"  where lab_id = "&amp;A127</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  National Research Institute for Radiobiology &amp; Radiohygiene , country =    where lab_id = 124</v>
       </c>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>125</v>
       </c>
@@ -8096,11 +8108,11 @@
         <v>48</v>
       </c>
       <c r="N128" t="str">
-        <f>"update lab set lab =  " &amp;C128&amp; " , country =  "&amp;H128&amp;"  where lab_id = "&amp;A128</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Radiological Sciences Institute - Division of Labs. &amp; Research , country =    where lab_id = 125</v>
       </c>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>126</v>
       </c>
@@ -8117,11 +8129,11 @@
         <v>433</v>
       </c>
       <c r="N129" t="str">
-        <f>"update lab set lab =  " &amp;C129&amp; " , country =  "&amp;H129&amp;"  where lab_id = "&amp;A129</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Department of Applied Chemistry - Technical University of Budapest , country =    where lab_id = 126</v>
       </c>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>127</v>
       </c>
@@ -8141,11 +8153,11 @@
         <v>48</v>
       </c>
       <c r="N130" t="str">
-        <f>"update lab set lab =  " &amp;C130&amp; " , country =  "&amp;H130&amp;"  where lab_id = "&amp;A130</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  University of Utah - School of Medicine , country =    where lab_id = 127</v>
       </c>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>128</v>
       </c>
@@ -8162,11 +8174,11 @@
         <v>433</v>
       </c>
       <c r="N131" t="str">
-        <f>"update lab set lab =  " &amp;C131&amp; " , country =  "&amp;H131&amp;"  where lab_id = "&amp;A131</f>
+        <f t="shared" si="1"/>
         <v>update lab set lab =  Central Research Institute for Physics of the Hungarian Academy of Sciences-Health Physics Dept. , country =    where lab_id = 128</v>
       </c>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>129</v>
       </c>
@@ -8183,11 +8195,11 @@
         <v>451</v>
       </c>
       <c r="N132" t="str">
-        <f>"update lab set lab =  " &amp;C132&amp; " , country =  "&amp;H132&amp;"  where lab_id = "&amp;A132</f>
+        <f t="shared" ref="N132:N195" si="2">"update lab set lab =  " &amp;C132&amp; " , country =  "&amp;H132&amp;"  where lab_id = "&amp;A132</f>
         <v>update lab set lab =  Environmental Studies Section - Health Physics Division , country =    where lab_id = 129</v>
       </c>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>130</v>
       </c>
@@ -8207,11 +8219,11 @@
         <v>456</v>
       </c>
       <c r="N133" t="str">
-        <f>"update lab set lab =  " &amp;C133&amp; " , country =  "&amp;H133&amp;"  where lab_id = "&amp;A133</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Research and Development Centre for Oceanology , country =    where lab_id = 130</v>
       </c>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>131</v>
       </c>
@@ -8231,11 +8243,11 @@
         <v>456</v>
       </c>
       <c r="N134" t="str">
-        <f>"update lab set lab =  " &amp;C134&amp; " , country =  "&amp;H134&amp;"  where lab_id = "&amp;A134</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Centre for the Application of Isotopes and Radiation , country =    where lab_id = 131</v>
       </c>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>132</v>
       </c>
@@ -8252,11 +8264,11 @@
         <v>464</v>
       </c>
       <c r="N135" t="str">
-        <f>"update lab set lab =  " &amp;C135&amp; " , country =  "&amp;H135&amp;"  where lab_id = "&amp;A135</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Radiation Protection Department - Atomic Energy Organization of Iran , country =    where lab_id = 132</v>
       </c>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>133</v>
       </c>
@@ -8276,11 +8288,11 @@
         <v>469</v>
       </c>
       <c r="N136" t="str">
-        <f>"update lab set lab =  " &amp;C136&amp; " , country =  "&amp;H136&amp;"  where lab_id = "&amp;A136</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Nuclear Research Centre - Department of Ecology , country =    where lab_id = 133</v>
       </c>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>134</v>
       </c>
@@ -8300,11 +8312,11 @@
         <v>48</v>
       </c>
       <c r="N137" t="str">
-        <f>"update lab set lab =  " &amp;C137&amp; " , country =  "&amp;H137&amp;"  where lab_id = "&amp;A137</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  University of Pittsburg - Radiochemical Analytical Laboratory , country =    where lab_id = 134</v>
       </c>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>135</v>
       </c>
@@ -8324,11 +8336,11 @@
         <v>478</v>
       </c>
       <c r="N138" t="str">
-        <f>"update lab set lab =  " &amp;C138&amp; " , country =  "&amp;H138&amp;"  where lab_id = "&amp;A138</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Nuclear Energy Board , country =    where lab_id = 135</v>
       </c>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>136</v>
       </c>
@@ -8348,11 +8360,11 @@
         <v>478</v>
       </c>
       <c r="N139" t="str">
-        <f>"update lab set lab =  " &amp;C139&amp; " , country =  "&amp;H139&amp;"  where lab_id = "&amp;A139</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Physics Dept. - University College , country =    where lab_id = 136</v>
       </c>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>137</v>
       </c>
@@ -8369,11 +8381,11 @@
         <v>485</v>
       </c>
       <c r="N140" t="str">
-        <f>"update lab set lab =  " &amp;C140&amp; " , country =  "&amp;H140&amp;"  where lab_id = "&amp;A140</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  E.N.E.A. - Centro Ricerche Nucl. della Trisaia , country =    where lab_id = 137</v>
       </c>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>138</v>
       </c>
@@ -8393,11 +8405,11 @@
         <v>485</v>
       </c>
       <c r="N141" t="str">
-        <f>"update lab set lab =  " &amp;C141&amp; " , country =  "&amp;H141&amp;"  where lab_id = "&amp;A141</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Laboratorio di Metrologia delle Radiazioni Ionizzanti , country =    where lab_id = 138</v>
       </c>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>139</v>
       </c>
@@ -8420,11 +8432,11 @@
         <v>485</v>
       </c>
       <c r="N142" t="str">
-        <f>"update lab set lab =  " &amp;C142&amp; " , country =  "&amp;H142&amp;"  where lab_id = "&amp;A142</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  E.N.E.A. - Centro Ricerche Energia Ambiente , country =    where lab_id = 139</v>
       </c>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>140</v>
       </c>
@@ -8441,11 +8453,11 @@
         <v>485</v>
       </c>
       <c r="N143" t="str">
-        <f>"update lab set lab =  " &amp;C143&amp; " , country =  "&amp;H143&amp;"  where lab_id = "&amp;A143</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  E.N.E.A. - C.R.E.  Brasimone , country =    where lab_id = 140</v>
       </c>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>141</v>
       </c>
@@ -8462,11 +8474,11 @@
         <v>485</v>
       </c>
       <c r="N144" t="str">
-        <f>"update lab set lab =  " &amp;C144&amp; " , country =  "&amp;H144&amp;"  where lab_id = "&amp;A144</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Istituto di Zoologia , country =    where lab_id = 141</v>
       </c>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>142</v>
       </c>
@@ -8483,11 +8495,11 @@
         <v>485</v>
       </c>
       <c r="N145" t="str">
-        <f>"update lab set lab =  " &amp;C145&amp; " , country =  "&amp;H145&amp;"  where lab_id = "&amp;A145</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Istituto di Ingegneria Nucleare Politecnico di Milano , country =    where lab_id = 142</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>143</v>
       </c>
@@ -8504,11 +8516,11 @@
         <v>485</v>
       </c>
       <c r="N146" t="str">
-        <f>"update lab set lab =  " &amp;C146&amp; " , country =  "&amp;H146&amp;"  where lab_id = "&amp;A146</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  University of Parma - Dipartimento di Biologia , country =    where lab_id = 143</v>
       </c>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>144</v>
       </c>
@@ -8525,11 +8537,11 @@
         <v>505</v>
       </c>
       <c r="N147" t="str">
-        <f>"update lab set lab =  " &amp;C147&amp; " , country =  "&amp;H147&amp;"  where lab_id = "&amp;A147</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Institute of Chemistry - University of Tsukuba , country =    where lab_id = 144</v>
       </c>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>145</v>
       </c>
@@ -8549,11 +8561,11 @@
         <v>505</v>
       </c>
       <c r="N148" t="str">
-        <f>"update lab set lab =  " &amp;C148&amp; " , country =  "&amp;H148&amp;"  where lab_id = "&amp;A148</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Power Reactor Nuclear Fuel - Development Corporation , country =    where lab_id = 145</v>
       </c>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>146</v>
       </c>
@@ -8573,11 +8585,11 @@
         <v>505</v>
       </c>
       <c r="N149" t="str">
-        <f>"update lab set lab =  " &amp;C149&amp; " , country =  "&amp;H149&amp;"  where lab_id = "&amp;A149</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Japan Atomic Energy Research Institute , country =    where lab_id = 146</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>147</v>
       </c>
@@ -8597,11 +8609,11 @@
         <v>505</v>
       </c>
       <c r="N150" t="str">
-        <f>"update lab set lab =  " &amp;C150&amp; " , country =  "&amp;H150&amp;"  where lab_id = "&amp;A150</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Japan Chemical Analysis Centre , country =    where lab_id = 147</v>
       </c>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>148</v>
       </c>
@@ -8621,11 +8633,11 @@
         <v>505</v>
       </c>
       <c r="N151" t="str">
-        <f>"update lab set lab =  " &amp;C151&amp; " , country =  "&amp;H151&amp;"  where lab_id = "&amp;A151</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  University of Tokyo - Ocean Research Institute , country =    where lab_id = 148</v>
       </c>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>149</v>
       </c>
@@ -8642,11 +8654,11 @@
         <v>505</v>
       </c>
       <c r="N152" t="str">
-        <f>"update lab set lab =  " &amp;C152&amp; " , country =  "&amp;H152&amp;"  where lab_id = "&amp;A152</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Kanazawa University - Faculty of Science , country =    where lab_id = 149</v>
       </c>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>150</v>
       </c>
@@ -8666,11 +8678,11 @@
         <v>48</v>
       </c>
       <c r="N153" t="str">
-        <f>"update lab set lab =  " &amp;C153&amp; " , country =  "&amp;H153&amp;"  where lab_id = "&amp;A153</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  M.A.D. Group -  HASRD - Oak Ridge National Laboratory , country =    where lab_id = 150</v>
       </c>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>151</v>
       </c>
@@ -8687,11 +8699,11 @@
         <v>505</v>
       </c>
       <c r="N154" t="str">
-        <f>"update lab set lab =  " &amp;C154&amp; " , country =  "&amp;H154&amp;"  where lab_id = "&amp;A154</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Hokkaido University - Faculty of Fisheries , country =    where lab_id = 151</v>
       </c>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>152</v>
       </c>
@@ -8711,11 +8723,11 @@
         <v>505</v>
       </c>
       <c r="N155" t="str">
-        <f>"update lab set lab =  " &amp;C155&amp; " , country =  "&amp;H155&amp;"  where lab_id = "&amp;A155</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Kanazawa University - Low Level Radioactivity Laboratory , country =    where lab_id = 152</v>
       </c>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>153</v>
       </c>
@@ -8732,11 +8744,11 @@
         <v>537</v>
       </c>
       <c r="N156" t="str">
-        <f>"update lab set lab =  " &amp;C156&amp; " , country =  "&amp;H156&amp;"  where lab_id = "&amp;A156</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Marine Biogeochemistry - Korea Ocean Research and Development Institute , country =    where lab_id = 153</v>
       </c>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>154</v>
       </c>
@@ -8756,11 +8768,11 @@
         <v>537</v>
       </c>
       <c r="N157" t="str">
-        <f>"update lab set lab =  " &amp;C157&amp; " , country =  "&amp;H157&amp;"  where lab_id = "&amp;A157</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  4th Division of Instruments - Korea Basic Science Centre , country =    where lab_id = 154</v>
       </c>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>155</v>
       </c>
@@ -8777,11 +8789,11 @@
         <v>545</v>
       </c>
       <c r="N158" t="str">
-        <f>"update lab set lab =  " &amp;C158&amp; " , country =  "&amp;H158&amp;"  where lab_id = "&amp;A158</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Kuwait Scientific Research Instit. - Central Analytical Laboratory , country =    where lab_id = 155</v>
       </c>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>156</v>
       </c>
@@ -8798,11 +8810,11 @@
         <v>545</v>
       </c>
       <c r="N159" t="str">
-        <f>"update lab set lab =  " &amp;C159&amp; " , country =  "&amp;H159&amp;"  where lab_id = "&amp;A159</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Ministry of Public Health - Environmental Protection Dept. , country =    where lab_id = 156</v>
       </c>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>157</v>
       </c>
@@ -8819,11 +8831,11 @@
         <v>552</v>
       </c>
       <c r="N160" t="str">
-        <f>"update lab set lab =  " &amp;C160&amp; " , country =  "&amp;H160&amp;"  where lab_id = "&amp;A160</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Conseil National de la Recherche Scientifique , country =    where lab_id = 157</v>
       </c>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>158</v>
       </c>
@@ -8840,11 +8852,11 @@
         <v>556</v>
       </c>
       <c r="N161" t="str">
-        <f>"update lab set lab =  " &amp;C161&amp; " , country =  "&amp;H161&amp;"  where lab_id = "&amp;A161</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Tajoura Research Centre , country =    where lab_id = 158</v>
       </c>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>159</v>
       </c>
@@ -8861,11 +8873,11 @@
         <v>560</v>
       </c>
       <c r="N162" t="str">
-        <f>"update lab set lab =  " &amp;C162&amp; " , country =  "&amp;H162&amp;"  where lab_id = "&amp;A162</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Nationwide Radiological Study , country =    where lab_id = 159</v>
       </c>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>160</v>
       </c>
@@ -8885,11 +8897,11 @@
         <v>565</v>
       </c>
       <c r="N163" t="str">
-        <f>"update lab set lab =  " &amp;C163&amp; " , country =  "&amp;H163&amp;"  where lab_id = "&amp;A163</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  C.N.S.N.S. - Env. Radiation Surveillance Branch , country =    where lab_id = 160</v>
       </c>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>161</v>
       </c>
@@ -8912,11 +8924,11 @@
         <v>48</v>
       </c>
       <c r="N164" t="str">
-        <f>"update lab set lab =  " &amp;C164&amp; " , country =  "&amp;H164&amp;"  where lab_id = "&amp;A164</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Radiological &amp; Env. Sciences Lab. - Department of Energy , country =    where lab_id = 161</v>
       </c>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>162</v>
       </c>
@@ -8936,11 +8948,11 @@
         <v>565</v>
       </c>
       <c r="N165" t="str">
-        <f>"update lab set lab =  " &amp;C165&amp; " , country =  "&amp;H165&amp;"  where lab_id = "&amp;A165</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Instituto de Investig. Electricas - Interior Internado Palmira , country =    where lab_id = 162</v>
       </c>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>163</v>
       </c>
@@ -8960,11 +8972,11 @@
         <v>565</v>
       </c>
       <c r="N166" t="str">
-        <f>"update lab set lab =  " &amp;C166&amp; " , country =  "&amp;H166&amp;"  where lab_id = "&amp;A166</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Laboratorio de Dosimetria y Monitoreo Ambiental - CFE - GCN , country =    where lab_id = 163</v>
       </c>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>164</v>
       </c>
@@ -8981,11 +8993,11 @@
         <v>582</v>
       </c>
       <c r="N167" t="str">
-        <f>"update lab set lab =  " &amp;C167&amp; " , country =  "&amp;H167&amp;"  where lab_id = "&amp;A167</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Laboratoire de Physique Nucléaire - Faculté des Sciences , country =    where lab_id = 164</v>
       </c>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>165</v>
       </c>
@@ -9005,11 +9017,11 @@
         <v>582</v>
       </c>
       <c r="N168" t="str">
-        <f>"update lab set lab =  " &amp;C168&amp; " , country =  "&amp;H168&amp;"  where lab_id = "&amp;A168</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Institut National Agronomique et Vétérinaire Hassan II , country =    where lab_id = 165</v>
       </c>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>166</v>
       </c>
@@ -9023,11 +9035,11 @@
         <v>582</v>
       </c>
       <c r="N169" t="str">
-        <f>"update lab set lab =  " &amp;C169&amp; " , country =  "&amp;H169&amp;"  where lab_id = "&amp;A169</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Ecole Mohammadia d Ingénieurs - Centre National de Génie Sanitaire , country =    where lab_id = 166</v>
       </c>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>167</v>
       </c>
@@ -9044,11 +9056,11 @@
         <v>589</v>
       </c>
       <c r="N170" t="str">
-        <f>"update lab set lab =  " &amp;C170&amp; " , country =  "&amp;H170&amp;"  where lab_id = "&amp;A170</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Netherlands Institute for Sea Research _N.I.O.Z._ , country =    where lab_id = 167</v>
       </c>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>168</v>
       </c>
@@ -9065,11 +9077,11 @@
         <v>48</v>
       </c>
       <c r="N171" t="str">
-        <f>"update lab set lab =  " &amp;C171&amp; " , country =  "&amp;H171&amp;"  where lab_id = "&amp;A171</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Nat. Air &amp; Radiat. Environmental Lab. - U.S. Environmental Protection Agency , country =    where lab_id = 168</v>
       </c>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>169</v>
       </c>
@@ -9086,11 +9098,11 @@
         <v>589</v>
       </c>
       <c r="N172" t="str">
-        <f>"update lab set lab =  " &amp;C172&amp; " , country =  "&amp;H172&amp;"  where lab_id = "&amp;A172</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  RIVM - Laboratory for Radiation Research , country =    where lab_id = 169</v>
       </c>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>170</v>
       </c>
@@ -9110,11 +9122,11 @@
         <v>589</v>
       </c>
       <c r="N173" t="str">
-        <f>"update lab set lab =  " &amp;C173&amp; " , country =  "&amp;H173&amp;"  where lab_id = "&amp;A173</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Radiochemistry Dept. of the Radiation Research Laboratory , country =    where lab_id = 170</v>
       </c>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>171</v>
       </c>
@@ -9131,11 +9143,11 @@
         <v>589</v>
       </c>
       <c r="N174" t="str">
-        <f>"update lab set lab =  " &amp;C174&amp; " , country =  "&amp;H174&amp;"  where lab_id = "&amp;A174</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Food Inspection Service , country =    where lab_id = 171</v>
       </c>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>172</v>
       </c>
@@ -9152,11 +9164,11 @@
         <v>589</v>
       </c>
       <c r="N175" t="str">
-        <f>"update lab set lab =  " &amp;C175&amp; " , country =  "&amp;H175&amp;"  where lab_id = "&amp;A175</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Rijksinstituut voor Volksgesondheid en Milieu Hygiene , country =    where lab_id = 172</v>
       </c>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>173</v>
       </c>
@@ -9173,11 +9185,11 @@
         <v>589</v>
       </c>
       <c r="N176" t="str">
-        <f>"update lab set lab =  " &amp;C176&amp; " , country =  "&amp;H176&amp;"  where lab_id = "&amp;A176</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Interfaculty Reactor Institute , country =    where lab_id = 173</v>
       </c>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>174</v>
       </c>
@@ -9197,11 +9209,11 @@
         <v>589</v>
       </c>
       <c r="N177" t="str">
-        <f>"update lab set lab =  " &amp;C177&amp; " , country =  "&amp;H177&amp;"  where lab_id = "&amp;A177</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Instit. for Inland Water Management and Waste Water Treatment , country =    where lab_id = 174</v>
       </c>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>175</v>
       </c>
@@ -9221,11 +9233,11 @@
         <v>589</v>
       </c>
       <c r="N178" t="str">
-        <f>"update lab set lab =  " &amp;C178&amp; " , country =  "&amp;H178&amp;"  where lab_id = "&amp;A178</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Netherlands Energy Research Foundation ECN , country =    where lab_id = 175</v>
       </c>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>176</v>
       </c>
@@ -9242,11 +9254,11 @@
         <v>589</v>
       </c>
       <c r="N179" t="str">
-        <f>"update lab set lab =  " &amp;C179&amp; " , country =  "&amp;H179&amp;"  where lab_id = "&amp;A179</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  RIKILT , country =    where lab_id = 176</v>
       </c>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>177</v>
       </c>
@@ -9260,11 +9272,11 @@
         <v>48</v>
       </c>
       <c r="N180" t="str">
-        <f>"update lab set lab =  " &amp;C180&amp; " , country =  "&amp;H180&amp;"  where lab_id = "&amp;A180</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Environmental Sciences Division - Oak Ridge National Laboratory , country =    where lab_id = 177</v>
       </c>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>178</v>
       </c>
@@ -9281,11 +9293,11 @@
         <v>622</v>
       </c>
       <c r="N181" t="str">
-        <f>"update lab set lab =  " &amp;C181&amp; " , country =  "&amp;H181&amp;"  where lab_id = "&amp;A181</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Institute of Nuclear Sciences , country =    where lab_id = 178</v>
       </c>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>179</v>
       </c>
@@ -9302,11 +9314,11 @@
         <v>626</v>
       </c>
       <c r="N182" t="str">
-        <f>"update lab set lab =  " &amp;C182&amp; " , country =  "&amp;H182&amp;"  where lab_id = "&amp;A182</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Centre for Energy Research and Training , country =    where lab_id = 179</v>
       </c>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>180</v>
       </c>
@@ -9323,11 +9335,11 @@
         <v>630</v>
       </c>
       <c r="N183" t="str">
-        <f>"update lab set lab =  " &amp;C183&amp; " , country =  "&amp;H183&amp;"  where lab_id = "&amp;A183</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Institute for Energy Technology Health and Safety Department , country =    where lab_id = 180</v>
       </c>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>181</v>
       </c>
@@ -9344,11 +9356,11 @@
         <v>630</v>
       </c>
       <c r="N184" t="str">
-        <f>"update lab set lab =  " &amp;C184&amp; " , country =  "&amp;H184&amp;"  where lab_id = "&amp;A184</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  National Institute for Radiation Hygiene , country =    where lab_id = 181</v>
       </c>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A185">
         <v>182</v>
       </c>
@@ -9365,11 +9377,11 @@
         <v>37</v>
       </c>
       <c r="N185" t="str">
-        <f>"update lab set lab =  " &amp;C185&amp; " , country =  "&amp;H185&amp;"  where lab_id = "&amp;A185</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  PINSTECH , country =    where lab_id = 182</v>
       </c>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A186">
         <v>183</v>
       </c>
@@ -9389,11 +9401,11 @@
         <v>640</v>
       </c>
       <c r="N186" t="str">
-        <f>"update lab set lab =  " &amp;C186&amp; " , country =  "&amp;H186&amp;"  where lab_id = "&amp;A186</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Instituto Peruano de Energia Nuclear , country =    where lab_id = 183</v>
       </c>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A187">
         <v>184</v>
       </c>
@@ -9413,11 +9425,11 @@
         <v>645</v>
       </c>
       <c r="N187" t="str">
-        <f>"update lab set lab =  " &amp;C187&amp; " , country =  "&amp;H187&amp;"  where lab_id = "&amp;A187</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Philippine Nuclear Research Inst. - Health Physics Research , country =    where lab_id = 184</v>
       </c>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A188">
         <v>185</v>
       </c>
@@ -9434,11 +9446,11 @@
         <v>645</v>
       </c>
       <c r="N188" t="str">
-        <f>"update lab set lab =  " &amp;C188&amp; " , country =  "&amp;H188&amp;"  where lab_id = "&amp;A188</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Radiological Services Section - Environmental Management Dept. , country =    where lab_id = 185</v>
       </c>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A189">
         <v>186</v>
       </c>
@@ -9455,11 +9467,11 @@
         <v>48</v>
       </c>
       <c r="N189" t="str">
-        <f>"update lab set lab =  " &amp;C189&amp; " , country =  "&amp;H189&amp;"  where lab_id = "&amp;A189</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Nuclear Reactor Laboratory - Ohio State University , country =    where lab_id = 186</v>
       </c>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A190">
         <v>187</v>
       </c>
@@ -9476,11 +9488,11 @@
         <v>31</v>
       </c>
       <c r="N190" t="str">
-        <f>"update lab set lab =  " &amp;C190&amp; " , country =  "&amp;H190&amp;"  where lab_id = "&amp;A190</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Institute of Oceanology - PAN , country =    where lab_id = 187</v>
       </c>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A191">
         <v>188</v>
       </c>
@@ -9500,11 +9512,11 @@
         <v>31</v>
       </c>
       <c r="N191" t="str">
-        <f>"update lab set lab =  " &amp;C191&amp; " , country =  "&amp;H191&amp;"  where lab_id = "&amp;A191</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Central Laboratory for Radiological Protection , country =    where lab_id = 188</v>
       </c>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A192">
         <v>189</v>
       </c>
@@ -9524,11 +9536,11 @@
         <v>31</v>
       </c>
       <c r="N192" t="str">
-        <f>"update lab set lab =  " &amp;C192&amp; " , country =  "&amp;H192&amp;"  where lab_id = "&amp;A192</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Department of Chemistry - Wyzsza Szkola Polniczo-Pedagocicna , country =    where lab_id = 189</v>
       </c>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A193">
         <v>190</v>
       </c>
@@ -9542,11 +9554,11 @@
         <v>48</v>
       </c>
       <c r="N193" t="str">
-        <f>"update lab set lab =  " &amp;C193&amp; " , country =  "&amp;H193&amp;"  where lab_id = "&amp;A193</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  University of Arkansas - Department of Chemistry , country =    where lab_id = 190</v>
       </c>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A194">
         <v>191</v>
       </c>
@@ -9566,11 +9578,11 @@
         <v>31</v>
       </c>
       <c r="N194" t="str">
-        <f>"update lab set lab =  " &amp;C194&amp; " , country =  "&amp;H194&amp;"  where lab_id = "&amp;A194</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Institute of Meteorology and Water Management , country =    where lab_id = 191</v>
       </c>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A195">
         <v>192</v>
       </c>
@@ -9590,11 +9602,11 @@
         <v>31</v>
       </c>
       <c r="N195" t="str">
-        <f>"update lab set lab =  " &amp;C195&amp; " , country =  "&amp;H195&amp;"  where lab_id = "&amp;A195</f>
+        <f t="shared" si="2"/>
         <v>update lab set lab =  Instytut Chemie Inorganicznej - Metallurgii Pierwiastkow Rzadkich , country =    where lab_id = 192</v>
       </c>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A196">
         <v>193</v>
       </c>
@@ -9614,11 +9626,11 @@
         <v>677</v>
       </c>
       <c r="N196" t="str">
-        <f>"update lab set lab =  " &amp;C196&amp; " , country =  "&amp;H196&amp;"  where lab_id = "&amp;A196</f>
+        <f t="shared" ref="N196:N259" si="3">"update lab set lab =  " &amp;C196&amp; " , country =  "&amp;H196&amp;"  where lab_id = "&amp;A196</f>
         <v>update lab set lab =  LNETI - Dept. de Protec. e Segur. Radiolog. , country =    where lab_id = 193</v>
       </c>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A197">
         <v>194</v>
       </c>
@@ -9635,11 +9647,11 @@
         <v>48</v>
       </c>
       <c r="N197" t="str">
-        <f>"update lab set lab =  " &amp;C197&amp; " , country =  "&amp;H197&amp;"  where lab_id = "&amp;A197</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  University of Southern California - Dept. of Geological Sciences , country =    where lab_id = 194</v>
       </c>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A198">
         <v>195</v>
       </c>
@@ -9659,11 +9671,11 @@
         <v>684</v>
       </c>
       <c r="N198" t="str">
-        <f>"update lab set lab =  " &amp;C198&amp; " , country =  "&amp;H198&amp;"  where lab_id = "&amp;A198</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Romanian Marine Research Institute - Radiobiology Unit , country =    where lab_id = 195</v>
       </c>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A199">
         <v>196</v>
       </c>
@@ -9677,11 +9689,11 @@
         <v>31</v>
       </c>
       <c r="N199" t="str">
-        <f>"update lab set lab =  " &amp;C199&amp; " , country =  "&amp;H199&amp;"  where lab_id = "&amp;A199</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Environmental Laboratory SPECTRA Ltd. _ul. Chopina 15_ , country =    where lab_id = 196</v>
       </c>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A200">
         <v>197</v>
       </c>
@@ -9698,11 +9710,11 @@
         <v>48</v>
       </c>
       <c r="N200" t="str">
-        <f>"update lab set lab =  " &amp;C200&amp; " , country =  "&amp;H200&amp;"  where lab_id = "&amp;A200</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Department of Radiology _339 MRB Building_ , country =    where lab_id = 197</v>
       </c>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A201">
         <v>198</v>
       </c>
@@ -9719,11 +9731,11 @@
         <v>684</v>
       </c>
       <c r="N201" t="str">
-        <f>"update lab set lab =  " &amp;C201&amp; " , country =  "&amp;H201&amp;"  where lab_id = "&amp;A201</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Laboratory for Air Pollution and Environmental Radioactivity , country =    where lab_id = 198</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A202">
         <v>199</v>
       </c>
@@ -9743,11 +9755,11 @@
         <v>48</v>
       </c>
       <c r="N202" t="str">
-        <f>"update lab set lab =  " &amp;C202&amp; " , country =  "&amp;H202&amp;"  where lab_id = "&amp;A202</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  D345 - Lab. of Inorg. &amp; Nuclear Chem. - Wadsworth Center for Labs &amp; Research , country =    where lab_id = 199</v>
       </c>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A203">
         <v>200</v>
       </c>
@@ -9764,11 +9776,11 @@
         <v>684</v>
       </c>
       <c r="N203" t="str">
-        <f>"update lab set lab =  " &amp;C203&amp; " , country =  "&amp;H203&amp;"  where lab_id = "&amp;A203</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Institute for Physics and Nuclear Engineering , country =    where lab_id = 200</v>
       </c>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A204">
         <v>201</v>
       </c>
@@ -9788,11 +9800,11 @@
         <v>684</v>
       </c>
       <c r="N204" t="str">
-        <f>"update lab set lab =  " &amp;C204&amp; " , country =  "&amp;H204&amp;"  where lab_id = "&amp;A204</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Scientific Research. - Institute of Food Chemistry , country =    where lab_id = 201</v>
       </c>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A205">
         <v>202</v>
       </c>
@@ -9812,11 +9824,11 @@
         <v>684</v>
       </c>
       <c r="N205" t="str">
-        <f>"update lab set lab =  " &amp;C205&amp; " , country =  "&amp;H205&amp;"  where lab_id = "&amp;A205</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Polytechnic Institute , country =    where lab_id = 202</v>
       </c>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A206">
         <v>203</v>
       </c>
@@ -9839,11 +9851,11 @@
         <v>48</v>
       </c>
       <c r="N206" t="str">
-        <f>"update lab set lab =  " &amp;C206&amp; " , country =  "&amp;H206&amp;"  where lab_id = "&amp;A206</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  E.M.L. - Department of Energy , country =    where lab_id = 203</v>
       </c>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A207">
         <v>204</v>
       </c>
@@ -9860,11 +9872,11 @@
         <v>684</v>
       </c>
       <c r="N207" t="str">
-        <f>"update lab set lab =  " &amp;C207&amp; " , country =  "&amp;H207&amp;"  where lab_id = "&amp;A207</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Radiation Hygiene Laboratory - Inst. for Hygiene &amp; Public Health , country =    where lab_id = 204</v>
       </c>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A208">
         <v>205</v>
       </c>
@@ -9890,11 +9902,11 @@
         <v>1579</v>
       </c>
       <c r="N208" t="str">
-        <f>"update lab set lab =  " &amp;C208&amp; " , country =  "&amp;H208&amp;"  where lab_id = "&amp;A208</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Environmental Radioactivity Lab. - Inst. of Environmental Research and Engineering , country =  40_0_552695  where lab_id = 205</v>
       </c>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A209">
         <v>206</v>
       </c>
@@ -9911,11 +9923,11 @@
         <v>684</v>
       </c>
       <c r="N209" t="str">
-        <f>"update lab set lab =  " &amp;C209&amp; " , country =  "&amp;H209&amp;"  where lab_id = "&amp;A209</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Institute of Atomic Physics , country =    where lab_id = 206</v>
       </c>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A210">
         <v>207</v>
       </c>
@@ -9932,11 +9944,11 @@
         <v>684</v>
       </c>
       <c r="N210" t="str">
-        <f>"update lab set lab =  " &amp;C210&amp; " , country =  "&amp;H210&amp;"  where lab_id = "&amp;A210</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Institute for Nucl. Power Reactors - Environmental Monitoring Laboratory , country =    where lab_id = 207</v>
       </c>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A211">
         <v>208</v>
       </c>
@@ -9950,11 +9962,11 @@
         <v>48</v>
       </c>
       <c r="N211" t="str">
-        <f>"update lab set lab =  " &amp;C211&amp; " , country =  "&amp;H211&amp;"  where lab_id = "&amp;A211</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  The Florida State University Department of Oceanography , country =    where lab_id = 208</v>
       </c>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A212">
         <v>209</v>
       </c>
@@ -9971,11 +9983,11 @@
         <v>177</v>
       </c>
       <c r="N212" t="str">
-        <f>"update lab set lab =  " &amp;C212&amp; " , country =  "&amp;H212&amp;"  where lab_id = "&amp;A212</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  National Radiological Protection Board , country =    where lab_id = 209</v>
       </c>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A213">
         <v>210</v>
       </c>
@@ -9992,11 +10004,11 @@
         <v>105</v>
       </c>
       <c r="N213" t="str">
-        <f>"update lab set lab =  " &amp;C213&amp; " , country =  "&amp;H213&amp;"  where lab_id = "&amp;A213</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Director of VNIIGEOINFORSISTEM _for V.V. Millera_ , country =    where lab_id = 210</v>
       </c>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A214">
         <v>211</v>
       </c>
@@ -10013,11 +10025,11 @@
         <v>105</v>
       </c>
       <c r="N214" t="str">
-        <f>"update lab set lab =  " &amp;C214&amp; " , country =  "&amp;H214&amp;"  where lab_id = "&amp;A214</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  V.G. Khlopin Radium Institute - Lab. of Environmental Radioactive Contamination Monitoring , country =    where lab_id = 211</v>
       </c>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A215">
         <v>212</v>
       </c>
@@ -10034,11 +10046,11 @@
         <v>105</v>
       </c>
       <c r="N215" t="str">
-        <f>"update lab set lab =  " &amp;C215&amp; " , country =  "&amp;H215&amp;"  where lab_id = "&amp;A215</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Polytechnic Institute - Geological Faculty , country =    where lab_id = 212</v>
       </c>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A216">
         <v>213</v>
       </c>
@@ -10055,11 +10067,11 @@
         <v>228</v>
       </c>
       <c r="N216" t="str">
-        <f>"update lab set lab =  " &amp;C216&amp; " , country =  "&amp;H216&amp;"  where lab_id = "&amp;A216</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Radiometry &amp; Radioecology Laboratory - Agriculture University , country =    where lab_id = 213</v>
       </c>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A217">
         <v>214</v>
       </c>
@@ -10073,11 +10085,11 @@
         <v>735</v>
       </c>
       <c r="N217" t="str">
-        <f>"update lab set lab =  " &amp;C217&amp; " , country =  "&amp;H217&amp;"  where lab_id = "&amp;A217</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Research Institute - University of Petroleum &amp; Minerals , country =    where lab_id = 214</v>
       </c>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A218">
         <v>215</v>
       </c>
@@ -10097,11 +10109,11 @@
         <v>739</v>
       </c>
       <c r="N218" t="str">
-        <f>"update lab set lab =  " &amp;C218&amp; " , country =  "&amp;H218&amp;"  where lab_id = "&amp;A218</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Institute of Occupational Health Radiological Protection , country =    where lab_id = 215</v>
       </c>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A219">
         <v>216</v>
       </c>
@@ -10118,11 +10130,11 @@
         <v>743</v>
       </c>
       <c r="N219" t="str">
-        <f>"update lab set lab =  " &amp;C219&amp; " , country =  "&amp;H219&amp;"  where lab_id = "&amp;A219</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Zavod SRS za varstvo pri delu , country =    where lab_id = 216</v>
       </c>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A220">
         <v>217</v>
       </c>
@@ -10142,11 +10154,11 @@
         <v>743</v>
       </c>
       <c r="N220" t="str">
-        <f>"update lab set lab =  " &amp;C220&amp; " , country =  "&amp;H220&amp;"  where lab_id = "&amp;A220</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Nuclear Institute  Jozef Stefan , country =    where lab_id = 217</v>
       </c>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A221">
         <v>218</v>
       </c>
@@ -10163,11 +10175,11 @@
         <v>743</v>
       </c>
       <c r="N221" t="str">
-        <f>"update lab set lab =  " &amp;C221&amp; " , country =  "&amp;H221&amp;"  where lab_id = "&amp;A221</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Importing Company IRIS , country =    where lab_id = 218</v>
       </c>
     </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A222">
         <v>219</v>
       </c>
@@ -10187,11 +10199,11 @@
         <v>752</v>
       </c>
       <c r="N222" t="str">
-        <f>"update lab set lab =  " &amp;C222&amp; " , country =  "&amp;H222&amp;"  where lab_id = "&amp;A222</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Environmental Studies Subdivision - Isotopes and Radiation Department , country =    where lab_id = 219</v>
       </c>
     </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A223">
         <v>220</v>
       </c>
@@ -10208,11 +10220,11 @@
         <v>752</v>
       </c>
       <c r="N223" t="str">
-        <f>"update lab set lab =  " &amp;C223&amp; " , country =  "&amp;H223&amp;"  where lab_id = "&amp;A223</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Council for Nuclear Safety , country =    where lab_id = 220</v>
       </c>
     </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A224">
         <v>221</v>
       </c>
@@ -10229,11 +10241,11 @@
         <v>752</v>
       </c>
       <c r="N224" t="str">
-        <f>"update lab set lab =  " &amp;C224&amp; " , country =  "&amp;H224&amp;"  where lab_id = "&amp;A224</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Koeberg Nuclear Power Station - Environmental Survey Laboratory , country =    where lab_id = 221</v>
       </c>
     </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A225">
         <v>222</v>
       </c>
@@ -10250,11 +10262,11 @@
         <v>177</v>
       </c>
       <c r="N225" t="str">
-        <f>"update lab set lab =  " &amp;C225&amp; " , country =  "&amp;H225&amp;"  where lab_id = "&amp;A225</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Cardiff City Analysts , country =    where lab_id = 222</v>
       </c>
     </row>
-    <row r="226" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A226">
         <v>223</v>
       </c>
@@ -10271,11 +10283,11 @@
         <v>765</v>
       </c>
       <c r="N226" t="str">
-        <f>"update lab set lab =  " &amp;C226&amp; " , country =  "&amp;H226&amp;"  where lab_id = "&amp;A226</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Universidad de Sevilla - Facultad de Fisica , country =    where lab_id = 223</v>
       </c>
     </row>
-    <row r="227" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A227">
         <v>224</v>
       </c>
@@ -10292,11 +10304,11 @@
         <v>37</v>
       </c>
       <c r="N227" t="str">
-        <f>"update lab set lab =  " &amp;C227&amp; " , country =  "&amp;H227&amp;"  where lab_id = "&amp;A227</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Nuclear Chemistry Division - Pakistan Institute of Nuclear Science and Technology , country =    where lab_id = 224</v>
       </c>
     </row>
-    <row r="228" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A228">
         <v>225</v>
       </c>
@@ -10313,11 +10325,11 @@
         <v>765</v>
       </c>
       <c r="N228" t="str">
-        <f>"update lab set lab =  " &amp;C228&amp; " , country =  "&amp;H228&amp;"  where lab_id = "&amp;A228</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  CIEMAT _I.M.A._ Ed.3 , country =    where lab_id = 225</v>
       </c>
     </row>
-    <row r="229" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A229">
         <v>226</v>
       </c>
@@ -10334,11 +10346,11 @@
         <v>765</v>
       </c>
       <c r="N229" t="str">
-        <f>"update lab set lab =  " &amp;C229&amp; " , country =  "&amp;H229&amp;"  where lab_id = "&amp;A229</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  University of Extremadura - Facultad de Veterinaria , country =    where lab_id = 226</v>
       </c>
     </row>
-    <row r="230" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A230">
         <v>227</v>
       </c>
@@ -10355,11 +10367,11 @@
         <v>765</v>
       </c>
       <c r="N230" t="str">
-        <f>"update lab set lab =  " &amp;C230&amp; " , country =  "&amp;H230&amp;"  where lab_id = "&amp;A230</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Instituto de Fisica Corpuscular , country =    where lab_id = 227</v>
       </c>
     </row>
-    <row r="231" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A231">
         <v>228</v>
       </c>
@@ -10379,11 +10391,11 @@
         <v>765</v>
       </c>
       <c r="N231" t="str">
-        <f>"update lab set lab =  " &amp;C231&amp; " , country =  "&amp;H231&amp;"  where lab_id = "&amp;A231</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Instituto de Tecnicas Energeticas - Univers. Politecnicas Barcelona , country =    where lab_id = 228</v>
       </c>
     </row>
-    <row r="232" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A232">
         <v>229</v>
       </c>
@@ -10403,11 +10415,11 @@
         <v>765</v>
       </c>
       <c r="N232" t="str">
-        <f>"update lab set lab =  " &amp;C232&amp; " , country =  "&amp;H232&amp;"  where lab_id = "&amp;A232</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Jefe Seccion Analisis y Medidas , country =    where lab_id = 229</v>
       </c>
     </row>
-    <row r="233" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A233">
         <v>230</v>
       </c>
@@ -10424,11 +10436,11 @@
         <v>765</v>
       </c>
       <c r="N233" t="str">
-        <f>"update lab set lab =  " &amp;C233&amp; " , country =  "&amp;H233&amp;"  where lab_id = "&amp;A233</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Servei de Fisica de les Radiacions - Universitat Autonoma de Barcelona , country =    where lab_id = 230</v>
       </c>
     </row>
-    <row r="234" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A234">
         <v>231</v>
       </c>
@@ -10445,11 +10457,11 @@
         <v>765</v>
       </c>
       <c r="N234" t="str">
-        <f>"update lab set lab =  " &amp;C234&amp; " , country =  "&amp;H234&amp;"  where lab_id = "&amp;A234</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Geotecnia y Cimientos S.A. - Poligono Industrial de Coslada , country =    where lab_id = 231</v>
       </c>
     </row>
-    <row r="235" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A235">
         <v>232</v>
       </c>
@@ -10466,11 +10478,11 @@
         <v>177</v>
       </c>
       <c r="N235" t="str">
-        <f>"update lab set lab =  " &amp;C235&amp; " , country =  "&amp;H235&amp;"  where lab_id = "&amp;A235</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  AEA - Environment and Energy Business , country =    where lab_id = 232</v>
       </c>
     </row>
-    <row r="236" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A236">
         <v>233</v>
       </c>
@@ -10487,11 +10499,11 @@
         <v>177</v>
       </c>
       <c r="N236" t="str">
-        <f>"update lab set lab =  " &amp;C236&amp; " , country =  "&amp;H236&amp;"  where lab_id = "&amp;A236</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Institute of Oceanographic Sciences , country =    where lab_id = 233</v>
       </c>
     </row>
-    <row r="237" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A237">
         <v>234</v>
       </c>
@@ -10511,11 +10523,11 @@
         <v>793</v>
       </c>
       <c r="N237" t="str">
-        <f>"update lab set lab =  " &amp;C237&amp; " , country =  "&amp;H237&amp;"  where lab_id = "&amp;A237</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Environmental Study Unit - National Aquatic Resources Agency , country =    where lab_id = 234</v>
       </c>
     </row>
-    <row r="238" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A238">
         <v>235</v>
       </c>
@@ -10532,11 +10544,11 @@
         <v>797</v>
       </c>
       <c r="N238" t="str">
-        <f>"update lab set lab =  " &amp;C238&amp; " , country =  "&amp;H238&amp;"  where lab_id = "&amp;A238</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Council for Conservation of Environment , country =    where lab_id = 235</v>
       </c>
     </row>
-    <row r="239" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A239">
         <v>236</v>
       </c>
@@ -10553,11 +10565,11 @@
         <v>797</v>
       </c>
       <c r="N239" t="str">
-        <f>"update lab set lab =  " &amp;C239&amp; " , country =  "&amp;H239&amp;"  where lab_id = "&amp;A239</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Ministry of Environment _Sultanate of Oman_ , country =    where lab_id = 236</v>
       </c>
     </row>
-    <row r="240" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A240">
         <v>237</v>
       </c>
@@ -10571,11 +10583,11 @@
         <v>99</v>
       </c>
       <c r="N240" t="str">
-        <f>"update lab set lab =  " &amp;C240&amp; " , country =  "&amp;H240&amp;"  where lab_id = "&amp;A240</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Lund University - Department of Radiation Physics , country =    where lab_id = 237</v>
       </c>
     </row>
-    <row r="241" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A241">
         <v>238</v>
       </c>
@@ -10601,11 +10613,11 @@
         <v>806</v>
       </c>
       <c r="N241" t="str">
-        <f>"update lab set lab =  " &amp;C241&amp; " , country =  "&amp;H241&amp;"  where lab_id = "&amp;A241</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  The Swedish University of Agricultural Sciences , country =  46 018 671000  where lab_id = 238</v>
       </c>
     </row>
-    <row r="242" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A242">
         <v>239</v>
       </c>
@@ -10625,11 +10637,11 @@
         <v>810</v>
       </c>
       <c r="N242" t="str">
-        <f>"update lab set lab =  " &amp;C242&amp; " , country =  "&amp;H242&amp;"  where lab_id = "&amp;A242</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Swedish Environment Protection Agency , country =  46 08 7991061  where lab_id = 239</v>
       </c>
     </row>
-    <row r="243" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A243">
         <v>240</v>
       </c>
@@ -10643,11 +10655,11 @@
         <v>99</v>
       </c>
       <c r="N243" t="str">
-        <f>"update lab set lab =  " &amp;C243&amp; " , country =  "&amp;H243&amp;"  where lab_id = "&amp;A243</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Studsvik Nuclear AB , country =    where lab_id = 240</v>
       </c>
     </row>
-    <row r="244" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A244">
         <v>241</v>
       </c>
@@ -10670,11 +10682,11 @@
         <v>99</v>
       </c>
       <c r="N244" t="str">
-        <f>"update lab set lab =  " &amp;C244&amp; " , country =  "&amp;H244&amp;"  where lab_id = "&amp;A244</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  The Swedish Radiation Protection Authority -  National Institute of Radiation Protection , country =    where lab_id = 241</v>
       </c>
     </row>
-    <row r="245" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A245">
         <v>242</v>
       </c>
@@ -10691,11 +10703,11 @@
         <v>177</v>
       </c>
       <c r="N245" t="str">
-        <f>"update lab set lab =  " &amp;C245&amp; " , country =  "&amp;H245&amp;"  where lab_id = "&amp;A245</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  N.R.P.B. - Scottish Centre , country =    where lab_id = 242</v>
       </c>
     </row>
-    <row r="246" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A246">
         <v>243</v>
       </c>
@@ -10715,11 +10727,11 @@
         <v>99</v>
       </c>
       <c r="N246" t="str">
-        <f>"update lab set lab =  " &amp;C246&amp; " , country =  "&amp;H246&amp;"  where lab_id = "&amp;A246</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  National Defence Research Institute , country =    where lab_id = 243</v>
       </c>
     </row>
-    <row r="247" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A247">
         <v>244</v>
       </c>
@@ -10736,11 +10748,11 @@
         <v>827</v>
       </c>
       <c r="N247" t="str">
-        <f>"update lab set lab =  " &amp;C247&amp; " , country =  "&amp;H247&amp;"  where lab_id = "&amp;A247</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Institut F.A. Forel - Université de Genève , country =    where lab_id = 244</v>
       </c>
     </row>
-    <row r="248" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A248">
         <v>245</v>
       </c>
@@ -10757,11 +10769,11 @@
         <v>827</v>
       </c>
       <c r="N248" t="str">
-        <f>"update lab set lab =  " &amp;C248&amp; " , country =  "&amp;H248&amp;"  where lab_id = "&amp;A248</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Paul Scherrer Institute , country =    where lab_id = 245</v>
       </c>
     </row>
-    <row r="249" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A249">
         <v>246</v>
       </c>
@@ -10778,11 +10790,11 @@
         <v>827</v>
       </c>
       <c r="N249" t="str">
-        <f>"update lab set lab =  " &amp;C249&amp; " , country =  "&amp;H249&amp;"  where lab_id = "&amp;A249</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Université de Neuchatel - Groupe Prosper , country =    where lab_id = 246</v>
       </c>
     </row>
-    <row r="250" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A250">
         <v>247</v>
       </c>
@@ -10799,11 +10811,11 @@
         <v>827</v>
       </c>
       <c r="N250" t="str">
-        <f>"update lab set lab =  " &amp;C250&amp; " , country =  "&amp;H250&amp;"  where lab_id = "&amp;A250</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  EAWAG - Abwasserreinigung u. Gewässerschutz , country =    where lab_id = 247</v>
       </c>
     </row>
-    <row r="251" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A251">
         <v>248</v>
       </c>
@@ -10823,11 +10835,11 @@
         <v>827</v>
       </c>
       <c r="N251" t="str">
-        <f>"update lab set lab =  " &amp;C251&amp; " , country =  "&amp;H251&amp;"  where lab_id = "&amp;A251</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Federal Office of Public Health - Radiation Surveillance Section , country =    where lab_id = 248</v>
       </c>
     </row>
-    <row r="252" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A252">
         <v>249</v>
       </c>
@@ -10847,11 +10859,11 @@
         <v>843</v>
       </c>
       <c r="N252" t="str">
-        <f>"update lab set lab =  " &amp;C252&amp; " , country =  "&amp;H252&amp;"  where lab_id = "&amp;A252</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Radiation Measurement Division _Bangkok_ , country =    where lab_id = 249</v>
       </c>
     </row>
-    <row r="253" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A253">
         <v>250</v>
       </c>
@@ -10868,11 +10880,11 @@
         <v>177</v>
       </c>
       <c r="N253" t="str">
-        <f>"update lab set lab =  " &amp;C253&amp; " , country =  "&amp;H253&amp;"  where lab_id = "&amp;A253</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Napier Polytechnic of Edinburgh , country =    where lab_id = 250</v>
       </c>
     </row>
-    <row r="254" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A254">
         <v>251</v>
       </c>
@@ -10892,11 +10904,11 @@
         <v>843</v>
       </c>
       <c r="N254" t="str">
-        <f>"update lab set lab =  " &amp;C254&amp; " , country =  "&amp;H254&amp;"  where lab_id = "&amp;A254</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Office of Atomic Energy for Peace - Env. Radiation Poll. Studies Sect. , country =    where lab_id = 251</v>
       </c>
     </row>
-    <row r="255" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A255">
         <v>252</v>
       </c>
@@ -10913,11 +10925,11 @@
         <v>852</v>
       </c>
       <c r="N255" t="str">
-        <f>"update lab set lab =  " &amp;C255&amp; " , country =  "&amp;H255&amp;"  where lab_id = "&amp;A255</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Institut National Scientifique et Technique d Océanographie et de Pêches , country =    where lab_id = 252</v>
       </c>
     </row>
-    <row r="256" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A256">
         <v>253</v>
       </c>
@@ -10934,11 +10946,11 @@
         <v>856</v>
       </c>
       <c r="N256" t="str">
-        <f>"update lab set lab =  " &amp;C256&amp; " , country =  "&amp;H256&amp;"  where lab_id = "&amp;A256</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Karadeniz Teknik Universitesi - Radiobiology Laboratory , country =    where lab_id = 253</v>
       </c>
     </row>
-    <row r="257" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A257">
         <v>254</v>
       </c>
@@ -10955,11 +10967,11 @@
         <v>856</v>
       </c>
       <c r="N257" t="str">
-        <f>"update lab set lab =  " &amp;C257&amp; " , country =  "&amp;H257&amp;"  where lab_id = "&amp;A257</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Cekmece Nuclear Research and Training Centre , country =    where lab_id = 254</v>
       </c>
     </row>
-    <row r="258" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A258">
         <v>255</v>
       </c>
@@ -10976,11 +10988,11 @@
         <v>856</v>
       </c>
       <c r="N258" t="str">
-        <f>"update lab set lab =  " &amp;C258&amp; " , country =  "&amp;H258&amp;"  where lab_id = "&amp;A258</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  Technical University of Istanbul - Institute for Nuclear Energy , country =    where lab_id = 255</v>
       </c>
     </row>
-    <row r="259" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A259">
         <v>256</v>
       </c>
@@ -11000,11 +11012,11 @@
         <v>856</v>
       </c>
       <c r="N259" t="str">
-        <f>"update lab set lab =  " &amp;C259&amp; " , country =  "&amp;H259&amp;"  where lab_id = "&amp;A259</f>
+        <f t="shared" si="3"/>
         <v>update lab set lab =  EGE University - Faculty of Science - Hydrology Laboratory , country =    where lab_id = 256</v>
       </c>
     </row>
-    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A260">
         <v>257</v>
       </c>
@@ -11021,11 +11033,11 @@
         <v>177</v>
       </c>
       <c r="N260" t="str">
-        <f>"update lab set lab =  " &amp;C260&amp; " , country =  "&amp;H260&amp;"  where lab_id = "&amp;A260</f>
+        <f t="shared" ref="N260:N323" si="4">"update lab set lab =  " &amp;C260&amp; " , country =  "&amp;H260&amp;"  where lab_id = "&amp;A260</f>
         <v>update lab set lab =  MAFF _Staplake Mount_ , country =    where lab_id = 257</v>
       </c>
     </row>
-    <row r="261" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A261">
         <v>258</v>
       </c>
@@ -11045,11 +11057,11 @@
         <v>177</v>
       </c>
       <c r="N261" t="str">
-        <f>"update lab set lab =  " &amp;C261&amp; " , country =  "&amp;H261&amp;"  where lab_id = "&amp;A261</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  N.R.P.B. _Northern Centre_ , country =    where lab_id = 258</v>
       </c>
     </row>
-    <row r="262" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A262">
         <v>259</v>
       </c>
@@ -11063,11 +11075,11 @@
         <v>177</v>
       </c>
       <c r="N262" t="str">
-        <f>"update lab set lab =  " &amp;C262&amp; " , country =  "&amp;H262&amp;"  where lab_id = "&amp;A262</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Department of Environmental Science - University of Lancaster , country =    where lab_id = 259</v>
       </c>
     </row>
-    <row r="263" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A263">
         <v>260</v>
       </c>
@@ -11084,11 +11096,11 @@
         <v>177</v>
       </c>
       <c r="N263" t="str">
-        <f>"update lab set lab =  " &amp;C263&amp; " , country =  "&amp;H263&amp;"  where lab_id = "&amp;A263</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  UKA.E.A. Technology - Dounreay Nuclear Power , country =    where lab_id = 260</v>
       </c>
     </row>
-    <row r="264" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A264">
         <v>261</v>
       </c>
@@ -11108,11 +11120,11 @@
         <v>177</v>
       </c>
       <c r="N264" t="str">
-        <f>"update lab set lab =  " &amp;C264&amp; " , country =  "&amp;H264&amp;"  where lab_id = "&amp;A264</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  British Nuclear Fuels plc - Chemical &amp; Metallurgical Services , country =    where lab_id = 261</v>
       </c>
     </row>
-    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A265">
         <v>262</v>
       </c>
@@ -11129,11 +11141,11 @@
         <v>177</v>
       </c>
       <c r="N265" t="str">
-        <f>"update lab set lab =  " &amp;C265&amp; " , country =  "&amp;H265&amp;"  where lab_id = "&amp;A265</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Central Electricity Generating Bd. - Scientific and Technical Branch , country =    where lab_id = 262</v>
       </c>
     </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A266">
         <v>263</v>
       </c>
@@ -11150,11 +11162,11 @@
         <v>177</v>
       </c>
       <c r="N266" t="str">
-        <f>"update lab set lab =  " &amp;C266&amp; " , country =  "&amp;H266&amp;"  where lab_id = "&amp;A266</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Department of Regional Chemist - Public Analyst and Agric. Analyst , country =    where lab_id = 263</v>
       </c>
     </row>
-    <row r="267" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A267">
         <v>264</v>
       </c>
@@ -11171,11 +11183,11 @@
         <v>177</v>
       </c>
       <c r="N267" t="str">
-        <f>"update lab set lab =  " &amp;C267&amp; " , country =  "&amp;H267&amp;"  where lab_id = "&amp;A267</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Regional Analyst s Lab. , country =    where lab_id = 264</v>
       </c>
     </row>
-    <row r="268" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A268">
         <v>265</v>
       </c>
@@ -11195,11 +11207,11 @@
         <v>177</v>
       </c>
       <c r="N268" t="str">
-        <f>"update lab set lab =  " &amp;C268&amp; " , country =  "&amp;H268&amp;"  where lab_id = "&amp;A268</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  MAFF _Directorate of Fisheries Research_ , country =    where lab_id = 265</v>
       </c>
     </row>
-    <row r="269" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A269">
         <v>266</v>
       </c>
@@ -11216,11 +11228,11 @@
         <v>177</v>
       </c>
       <c r="N269" t="str">
-        <f>"update lab set lab =  " &amp;C269&amp; " , country =  "&amp;H269&amp;"  where lab_id = "&amp;A269</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Somerset County Council - County Laboratory , country =    where lab_id = 266</v>
       </c>
     </row>
-    <row r="270" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A270">
         <v>267</v>
       </c>
@@ -11240,11 +11252,11 @@
         <v>177</v>
       </c>
       <c r="N270" t="str">
-        <f>"update lab set lab =  " &amp;C270&amp; " , country =  "&amp;H270&amp;"  where lab_id = "&amp;A270</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Division of Radiation Science and Acoustics , country =    where lab_id = 267</v>
       </c>
     </row>
-    <row r="271" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A271">
         <v>268</v>
       </c>
@@ -11264,11 +11276,11 @@
         <v>177</v>
       </c>
       <c r="N271" t="str">
-        <f>"update lab set lab =  " &amp;C271&amp; " , country =  "&amp;H271&amp;"  where lab_id = "&amp;A271</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Institute of Environmental and Biological Sciences , country =    where lab_id = 268</v>
       </c>
     </row>
-    <row r="272" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A272">
         <v>269</v>
       </c>
@@ -11288,11 +11300,11 @@
         <v>177</v>
       </c>
       <c r="N272" t="str">
-        <f>"update lab set lab =  " &amp;C272&amp; " , country =  "&amp;H272&amp;"  where lab_id = "&amp;A272</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Humberside County , country =    where lab_id = 269</v>
       </c>
     </row>
-    <row r="273" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A273">
         <v>270</v>
       </c>
@@ -11306,11 +11318,11 @@
         <v>177</v>
       </c>
       <c r="N273" t="str">
-        <f>"update lab set lab =  " &amp;C273&amp; " , country =  "&amp;H273&amp;"  where lab_id = "&amp;A273</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Institute of Terrestrial Ecology - Merlewood Research Station , country =    where lab_id = 270</v>
       </c>
     </row>
-    <row r="274" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A274">
         <v>271</v>
       </c>
@@ -11324,11 +11336,11 @@
         <v>177</v>
       </c>
       <c r="N274" t="str">
-        <f>"update lab set lab =  " &amp;C274&amp; " , country =  "&amp;H274&amp;"  where lab_id = "&amp;A274</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Chemistry Department - University of Glasgow , country =    where lab_id = 271</v>
       </c>
     </row>
-    <row r="275" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A275">
         <v>272</v>
       </c>
@@ -11348,11 +11360,11 @@
         <v>203</v>
       </c>
       <c r="N275" t="str">
-        <f>"update lab set lab =  " &amp;C275&amp; " , country =  "&amp;H275&amp;"  where lab_id = "&amp;A275</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Lab. de Tecnicas Analit. Nucleares - Depart. de Radioanalysis y Tecnicas Nucleares , country =    where lab_id = 272</v>
       </c>
     </row>
-    <row r="276" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A276">
         <v>273</v>
       </c>
@@ -11366,11 +11378,11 @@
         <v>340</v>
       </c>
       <c r="N276" t="str">
-        <f>"update lab set lab =  " &amp;C276&amp; " , country =  "&amp;H276&amp;"  where lab_id = "&amp;A276</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Bundesamt für Seeschiffahrt und Hydrographie , country =    where lab_id = 273</v>
       </c>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A277">
         <v>274</v>
       </c>
@@ -11387,11 +11399,11 @@
         <v>268</v>
       </c>
       <c r="N277" t="str">
-        <f>"update lab set lab =  " &amp;C277&amp; " , country =  "&amp;H277&amp;"  where lab_id = "&amp;A277</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Kiev State University - Inter-Branch Institute of Personal Retraining , country =    where lab_id = 274</v>
       </c>
     </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A278">
         <v>275</v>
       </c>
@@ -11411,11 +11423,11 @@
         <v>268</v>
       </c>
       <c r="N278" t="str">
-        <f>"update lab set lab =  " &amp;C278&amp; " , country =  "&amp;H278&amp;"  where lab_id = "&amp;A278</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  All-Union Scientific Centre of Radiation Medicine , country =    where lab_id = 275</v>
       </c>
     </row>
-    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A279">
         <v>276</v>
       </c>
@@ -11435,11 +11447,11 @@
         <v>177</v>
       </c>
       <c r="N279" t="str">
-        <f>"update lab set lab =  " &amp;C279&amp; " , country =  "&amp;H279&amp;"  where lab_id = "&amp;A279</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Scottish Universities Research and Nuclear Centre , country =    where lab_id = 276</v>
       </c>
     </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A280">
         <v>277</v>
       </c>
@@ -11453,11 +11465,11 @@
         <v>105</v>
       </c>
       <c r="N280" t="str">
-        <f>"update lab set lab =  " &amp;C280&amp; " , country =  "&amp;H280&amp;"  where lab_id = "&amp;A280</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Russian Federation _X + 1_ , country =    where lab_id = 277</v>
       </c>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A281">
         <v>278</v>
       </c>
@@ -11471,11 +11483,11 @@
         <v>177</v>
       </c>
       <c r="N281" t="str">
-        <f>"update lab set lab =  " &amp;C281&amp; " , country =  "&amp;H281&amp;"  where lab_id = "&amp;A281</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Ministry of Agriculture, Fisheries and Food , country =    where lab_id = 278</v>
       </c>
     </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A282">
         <v>279</v>
       </c>
@@ -11492,11 +11504,11 @@
         <v>565</v>
       </c>
       <c r="N282" t="str">
-        <f>"update lab set lab =  " &amp;C282&amp; " , country =  "&amp;H282&amp;"  where lab_id = "&amp;A282</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Technological Institute of Mazatlán , country =    where lab_id = 279</v>
       </c>
     </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A283">
         <v>280</v>
       </c>
@@ -11513,11 +11525,11 @@
         <v>505</v>
       </c>
       <c r="N283" t="str">
-        <f>"update lab set lab =  " &amp;C283&amp; " , country =  "&amp;H283&amp;"  where lab_id = "&amp;A283</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Ehime Prefectural Institute of Public Health and Environmental Science , country =    where lab_id = 280</v>
       </c>
     </row>
-    <row r="284" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A284">
         <v>281</v>
       </c>
@@ -11531,11 +11543,11 @@
         <v>630</v>
       </c>
       <c r="N284" t="str">
-        <f>"update lab set lab =  " &amp;C284&amp; " , country =  "&amp;H284&amp;"  where lab_id = "&amp;A284</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Norwegian Polar Institute , country =    where lab_id = 281</v>
       </c>
     </row>
-    <row r="285" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A285">
         <v>282</v>
       </c>
@@ -11558,11 +11570,11 @@
         <v>941</v>
       </c>
       <c r="N285" t="str">
-        <f>"update lab set lab =  " &amp;C285&amp; " , country =  "&amp;H285&amp;"  where lab_id = "&amp;A285</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Woods Hole Oceanographic Institution , country =    where lab_id = 282</v>
       </c>
     </row>
-    <row r="286" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A286">
         <v>283</v>
       </c>
@@ -11582,11 +11594,11 @@
         <v>109</v>
       </c>
       <c r="N286" t="str">
-        <f>"update lab set lab =  " &amp;C286&amp; " , country =  "&amp;H286&amp;"  where lab_id = "&amp;A286</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Indústrias Nucleares do Brasil , country =    where lab_id = 283</v>
       </c>
     </row>
-    <row r="287" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A287">
         <v>284</v>
       </c>
@@ -11603,11 +11615,11 @@
         <v>83</v>
       </c>
       <c r="N287" t="str">
-        <f>"update lab set lab =  " &amp;C287&amp; " , country =  "&amp;H287&amp;"  where lab_id = "&amp;A287</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Bangladesh Atomic Energy Commission - Radioactivity Testing and Monitoring Laboratory , country =    where lab_id = 284</v>
       </c>
     </row>
-    <row r="288" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A288">
         <v>285</v>
       </c>
@@ -11624,11 +11636,11 @@
         <v>451</v>
       </c>
       <c r="N288" t="str">
-        <f>"update lab set lab =  " &amp;C288&amp; " , country =  "&amp;H288&amp;"  where lab_id = "&amp;A288</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Scott Christian College - Department of Zoology and Research Centre , country =    where lab_id = 285</v>
       </c>
     </row>
-    <row r="289" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A289">
         <v>286</v>
       </c>
@@ -11645,11 +11657,11 @@
         <v>451</v>
       </c>
       <c r="N289" t="str">
-        <f>"update lab set lab =  " &amp;C289&amp; " , country =  "&amp;H289&amp;"  where lab_id = "&amp;A289</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  JSS University - Center for Water and Health , country =    where lab_id = 286</v>
       </c>
     </row>
-    <row r="290" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A290">
         <v>287</v>
       </c>
@@ -11666,11 +11678,11 @@
         <v>451</v>
       </c>
       <c r="N290" t="str">
-        <f>"update lab set lab =  " &amp;C290&amp; " , country =  "&amp;H290&amp;"  where lab_id = "&amp;A290</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Sadakathullah Appa College - Department of Advanced Zoology and Biotechnology , country =    where lab_id = 287</v>
       </c>
     </row>
-    <row r="291" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A291">
         <v>288</v>
       </c>
@@ -11687,11 +11699,11 @@
         <v>451</v>
       </c>
       <c r="N291" t="str">
-        <f>"update lab set lab =  " &amp;C291&amp; " , country =  "&amp;H291&amp;"  where lab_id = "&amp;A291</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  ICAR-Central Institute of Fisheries Education , country =    where lab_id = 288</v>
       </c>
     </row>
-    <row r="292" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A292">
         <v>289</v>
       </c>
@@ -11705,11 +11717,11 @@
         <v>962</v>
       </c>
       <c r="N292" t="str">
-        <f>"update lab set lab =  " &amp;C292&amp; " , country =  "&amp;H292&amp;"  where lab_id = "&amp;A292</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Yarmouk University - Faculty of Science , country =    where lab_id = 289</v>
       </c>
     </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A293">
         <v>290</v>
       </c>
@@ -11726,11 +11738,11 @@
         <v>966</v>
       </c>
       <c r="N293" t="str">
-        <f>"update lab set lab =  " &amp;C293&amp; " , country =  "&amp;H293&amp;"  where lab_id = "&amp;A293</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Universiti Teknologi MARA - Faculty of Applied Sciences , country =    where lab_id = 290</v>
       </c>
     </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A294">
         <v>291</v>
       </c>
@@ -11747,11 +11759,11 @@
         <v>48</v>
       </c>
       <c r="N294" t="str">
-        <f>"update lab set lab =  " &amp;C294&amp; " , country =  "&amp;H294&amp;"  where lab_id = "&amp;A294</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  University of New York - Institute of Environmental Medicine , country =    where lab_id = 291</v>
       </c>
     </row>
-    <row r="295" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A295">
         <v>292</v>
       </c>
@@ -11768,11 +11780,11 @@
         <v>966</v>
       </c>
       <c r="N295" t="str">
-        <f>"update lab set lab =  " &amp;C295&amp; " , country =  "&amp;H295&amp;"  where lab_id = "&amp;A295</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Sunway University - School of Healthcare and Medical Sciences , country =    where lab_id = 292</v>
       </c>
     </row>
-    <row r="296" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A296">
         <v>293</v>
       </c>
@@ -11789,11 +11801,11 @@
         <v>505</v>
       </c>
       <c r="N296" t="str">
-        <f>"update lab set lab =  " &amp;C296&amp; " , country =  "&amp;H296&amp;"  where lab_id = "&amp;A296</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Kyushu University - Radioisotope Center , country =    where lab_id = 293</v>
       </c>
     </row>
-    <row r="297" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A297">
         <v>294</v>
       </c>
@@ -11807,11 +11819,11 @@
         <v>537</v>
       </c>
       <c r="N297" t="str">
-        <f>"update lab set lab =  " &amp;C297&amp; " , country =  "&amp;H297&amp;"  where lab_id = "&amp;A297</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Korea Research Institute of Standards and Science , country =    where lab_id = 294</v>
       </c>
     </row>
-    <row r="298" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A298">
         <v>295</v>
       </c>
@@ -11825,11 +11837,11 @@
         <v>158</v>
       </c>
       <c r="N298" t="str">
-        <f>"update lab set lab =  " &amp;C298&amp; " , country =  "&amp;H298&amp;"  where lab_id = "&amp;A298</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Tsinghua University - Department of Engineering Physics , country =    where lab_id = 295</v>
       </c>
     </row>
-    <row r="299" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A299">
         <v>296</v>
       </c>
@@ -11846,11 +11858,11 @@
         <v>505</v>
       </c>
       <c r="N299" t="str">
-        <f>"update lab set lab =  " &amp;C299&amp; " , country =  "&amp;H299&amp;"  where lab_id = "&amp;A299</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Toho University - Department of Biomolecular Science , country =    where lab_id = 296</v>
       </c>
     </row>
-    <row r="300" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A300">
         <v>297</v>
       </c>
@@ -11867,11 +11879,11 @@
         <v>48</v>
       </c>
       <c r="N300" t="str">
-        <f>"update lab set lab =  " &amp;C300&amp; " , country =  "&amp;H300&amp;"  where lab_id = "&amp;A300</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Stanford University - Hopkins Marine Station , country =    where lab_id = 297</v>
       </c>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A301">
         <v>298</v>
       </c>
@@ -11885,11 +11897,11 @@
         <v>158</v>
       </c>
       <c r="N301" t="str">
-        <f>"update lab set lab =  " &amp;C301&amp; " , country =  "&amp;H301&amp;"  where lab_id = "&amp;A301</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  National Institute for Radiological Protection , country =    where lab_id = 298</v>
       </c>
     </row>
-    <row r="302" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A302">
         <v>299</v>
       </c>
@@ -11906,11 +11918,11 @@
         <v>48</v>
       </c>
       <c r="N302" t="str">
-        <f>"update lab set lab =  " &amp;C302&amp; " , country =  "&amp;H302&amp;"  where lab_id = "&amp;A302</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Stony Brook University - School of Marine and Atmospheric Sciences , country =    where lab_id = 299</v>
       </c>
     </row>
-    <row r="303" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A303">
         <v>300</v>
       </c>
@@ -11927,11 +11939,11 @@
         <v>856</v>
       </c>
       <c r="N303" t="str">
-        <f>"update lab set lab =  " &amp;C303&amp; " , country =  "&amp;H303&amp;"  where lab_id = "&amp;A303</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Kirklareli University - Department of Physics , country =    where lab_id = 300</v>
       </c>
     </row>
-    <row r="304" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A304">
         <v>301</v>
       </c>
@@ -11948,11 +11960,11 @@
         <v>277</v>
       </c>
       <c r="N304" t="str">
-        <f>"update lab set lab =  " &amp;C304&amp; " , country =  "&amp;H304&amp;"  where lab_id = "&amp;A304</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Radiation and Nuclear Safety Authority , country =    where lab_id = 301</v>
       </c>
     </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A305">
         <v>302</v>
       </c>
@@ -11969,11 +11981,11 @@
         <v>765</v>
       </c>
       <c r="N305" t="str">
-        <f>"update lab set lab =  " &amp;C305&amp; " , country =  "&amp;H305&amp;"  where lab_id = "&amp;A305</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Universidad de Sevilla - Centro de Investigación, Tecnología e Innovación , country =    where lab_id = 302</v>
       </c>
     </row>
-    <row r="306" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A306">
         <v>303</v>
       </c>
@@ -11990,11 +12002,11 @@
         <v>765</v>
       </c>
       <c r="N306" t="str">
-        <f>"update lab set lab =  " &amp;C306&amp; " , country =  "&amp;H306&amp;"  where lab_id = "&amp;A306</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Universitat Rovira i Virgili - School of Medicine , country =    where lab_id = 303</v>
       </c>
     </row>
-    <row r="307" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A307">
         <v>304</v>
       </c>
@@ -12011,11 +12023,11 @@
         <v>125</v>
       </c>
       <c r="N307" t="str">
-        <f>"update lab set lab =  " &amp;C307&amp; " , country =  "&amp;H307&amp;"  where lab_id = "&amp;A307</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Institute for Nuclear Research and Nuclear Energy - Radiochemistry and Radioecology Department , country =    where lab_id = 304</v>
       </c>
     </row>
-    <row r="308" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A308">
         <v>305</v>
       </c>
@@ -12032,11 +12044,11 @@
         <v>856</v>
       </c>
       <c r="N308" t="str">
-        <f>"update lab set lab =  " &amp;C308&amp; " , country =  "&amp;H308&amp;"  where lab_id = "&amp;A308</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Technology Development Department , country =    where lab_id = 305</v>
       </c>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A309">
         <v>306</v>
       </c>
@@ -12053,11 +12065,11 @@
         <v>582</v>
       </c>
       <c r="N309" t="str">
-        <f>"update lab set lab =  " &amp;C309&amp; " , country =  "&amp;H309&amp;"  where lab_id = "&amp;A309</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =   Ibn Tofail University - Department of Physics , country =    where lab_id = 306</v>
       </c>
     </row>
-    <row r="310" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A310">
         <v>307</v>
       </c>
@@ -12071,11 +12083,11 @@
         <v>856</v>
       </c>
       <c r="N310" t="str">
-        <f>"update lab set lab =  " &amp;C310&amp; " , country =  "&amp;H310&amp;"  where lab_id = "&amp;A310</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Akdeniz University - Department of Aquaculture, Faculty of Fisheries , country =    where lab_id = 307</v>
       </c>
     </row>
-    <row r="311" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A311">
         <v>308</v>
       </c>
@@ -12089,11 +12101,11 @@
         <v>966</v>
       </c>
       <c r="N311" t="str">
-        <f>"update lab set lab =  " &amp;C311&amp; " , country =  "&amp;H311&amp;"  where lab_id = "&amp;A311</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  University of Malaya - Department of Physics , country =    where lab_id = 308</v>
       </c>
     </row>
-    <row r="312" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A312">
         <v>309</v>
       </c>
@@ -12107,11 +12119,11 @@
         <v>22</v>
       </c>
       <c r="N312" t="str">
-        <f>"update lab set lab =  " &amp;C312&amp; " , country =  "&amp;H312&amp;"  where lab_id = "&amp;A312</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Morsli Abdallah University - Department of Natural Sciences and Life , country =    where lab_id = 309</v>
       </c>
     </row>
-    <row r="313" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A313">
         <v>310</v>
       </c>
@@ -12128,11 +12140,11 @@
         <v>505</v>
       </c>
       <c r="N313" t="str">
-        <f>"update lab set lab =  " &amp;C313&amp; " , country =  "&amp;H313&amp;"  where lab_id = "&amp;A313</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Marine Biological Research Institute of Japan Co., LTD , country =    where lab_id = 310</v>
       </c>
     </row>
-    <row r="314" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A314">
         <v>311</v>
       </c>
@@ -12152,11 +12164,11 @@
         <v>48</v>
       </c>
       <c r="N314" t="str">
-        <f>"update lab set lab =  " &amp;C314&amp; " , country =  "&amp;H314&amp;"  where lab_id = "&amp;A314</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  University of California - Division of Environmental Studies , country =    where lab_id = 311</v>
       </c>
     </row>
-    <row r="315" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A315">
         <v>312</v>
       </c>
@@ -12173,11 +12185,11 @@
         <v>505</v>
       </c>
       <c r="N315" t="str">
-        <f>"update lab set lab =  " &amp;C315&amp; " , country =  "&amp;H315&amp;"  where lab_id = "&amp;A315</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Tokyo University of Marine Science and Technology , country =    where lab_id = 312</v>
       </c>
     </row>
-    <row r="316" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A316">
         <v>313</v>
       </c>
@@ -12191,11 +12203,11 @@
         <v>340</v>
       </c>
       <c r="N316" t="str">
-        <f>"update lab set lab =  " &amp;C316&amp; " , country =  "&amp;H316&amp;"  where lab_id = "&amp;A316</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Deutsch Hydrographisches Inst , country =    where lab_id = 313</v>
       </c>
     </row>
-    <row r="317" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A317">
         <v>317</v>
       </c>
@@ -12209,11 +12221,11 @@
         <v>48</v>
       </c>
       <c r="N317" t="str">
-        <f>"update lab set lab =  " &amp;C317&amp; " , country =  "&amp;H317&amp;"  where lab_id = "&amp;A317</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  University of Miami _C-14 lab_ , country =    where lab_id = 317</v>
       </c>
     </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A318">
         <v>318</v>
       </c>
@@ -12227,11 +12239,11 @@
         <v>48</v>
       </c>
       <c r="N318" t="str">
-        <f>"update lab set lab =  " &amp;C318&amp; " , country =  "&amp;H318&amp;"  where lab_id = "&amp;A318</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  University of Washington _C-14 lab_ , country =    where lab_id = 318</v>
       </c>
     </row>
-    <row r="319" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A319">
         <v>319</v>
       </c>
@@ -12245,11 +12257,11 @@
         <v>105</v>
       </c>
       <c r="N319" t="str">
-        <f>"update lab set lab =  " &amp;C319&amp; " , country =  "&amp;H319&amp;"  where lab_id = "&amp;A319</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  SPA Typhoon , country =    where lab_id = 319</v>
       </c>
     </row>
-    <row r="320" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A320">
         <v>320</v>
       </c>
@@ -12263,11 +12275,11 @@
         <v>630</v>
       </c>
       <c r="N320" t="str">
-        <f>"update lab set lab =  " &amp;C320&amp; " , country =  "&amp;H320&amp;"  where lab_id = "&amp;A320</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Radiation Protection Authority , country =    where lab_id = 320</v>
       </c>
     </row>
-    <row r="321" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A321">
         <v>321</v>
       </c>
@@ -12293,11 +12305,11 @@
         <v>1524</v>
       </c>
       <c r="N321" t="str">
-        <f>"update lab set lab =  " &amp;C321&amp; " , country =  "&amp;H321&amp;"  where lab_id = "&amp;A321</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Estonian Meteorological and Hydrological Institute , country =    where lab_id = 321</v>
       </c>
     </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A322">
         <v>322</v>
       </c>
@@ -12332,11 +12344,11 @@
         <v>1048</v>
       </c>
       <c r="N322" t="str">
-        <f>"update lab set lab =  " &amp;C322&amp; " , country =  "&amp;H322&amp;"  where lab_id = "&amp;A322</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Estonian Radiation Protection Centre , country =  372 660 33  where lab_id = 322</v>
       </c>
     </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A323">
         <v>323</v>
       </c>
@@ -12350,11 +12362,11 @@
         <v>1051</v>
       </c>
       <c r="N323" t="str">
-        <f>"update lab set lab =  " &amp;C323&amp; " , country =  "&amp;H323&amp;"  where lab_id = "&amp;A323</f>
+        <f t="shared" si="4"/>
         <v>update lab set lab =  Joint Research Center , country =    where lab_id = 323</v>
       </c>
     </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A324">
         <v>324</v>
       </c>
@@ -12368,11 +12380,11 @@
         <v>1051</v>
       </c>
       <c r="N324" t="str">
-        <f>"update lab set lab =  " &amp;C324&amp; " , country =  "&amp;H324&amp;"  where lab_id = "&amp;A324</f>
+        <f t="shared" ref="N324:N387" si="5">"update lab set lab =  " &amp;C324&amp; " , country =  "&amp;H324&amp;"  where lab_id = "&amp;A324</f>
         <v>update lab set lab =  Lithuanian Environmental Protection Agency , country =    where lab_id = 324</v>
       </c>
     </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A325">
         <v>325</v>
       </c>
@@ -12389,11 +12401,11 @@
         <v>1526</v>
       </c>
       <c r="N325" t="str">
-        <f>"update lab set lab =  " &amp;C325&amp; " , country =  "&amp;H325&amp;"  where lab_id = "&amp;A325</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Latvian Environment Agency , country =    where lab_id = 325</v>
       </c>
     </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A326">
         <v>326</v>
       </c>
@@ -12407,11 +12419,11 @@
         <v>1056</v>
       </c>
       <c r="N326" t="str">
-        <f>"update lab set lab =  " &amp;C326&amp; " , country =  "&amp;H326&amp;"  where lab_id = "&amp;A326</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Environmental Data Center of Latvia , country =    where lab_id = 326</v>
       </c>
     </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A327">
         <v>327</v>
       </c>
@@ -12425,11 +12437,11 @@
         <v>1056</v>
       </c>
       <c r="N327" t="str">
-        <f>"update lab set lab =  " &amp;C327&amp; " , country =  "&amp;H327&amp;"  where lab_id = "&amp;A327</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Lielriga Regional Environmental Board , country =    where lab_id = 327</v>
       </c>
     </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A328">
         <v>328</v>
       </c>
@@ -12455,11 +12467,11 @@
         <v>1066</v>
       </c>
       <c r="N328" t="str">
-        <f>"update lab set lab =  " &amp;C328&amp; " , country =  "&amp;H328&amp;"  where lab_id = "&amp;A328</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Scientific Institute of public health , country =  32.2.642.56.62  where lab_id = 328</v>
       </c>
     </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A329">
         <v>329</v>
       </c>
@@ -12485,11 +12497,11 @@
         <v>1073</v>
       </c>
       <c r="N329" t="str">
-        <f>"update lab set lab =  " &amp;C329&amp; " , country =  "&amp;H329&amp;"  where lab_id = "&amp;A329</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Risø National Laboratory - The Radiation Research Department , country =  45 4677 5340  where lab_id = 329</v>
       </c>
     </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A330">
         <v>330</v>
       </c>
@@ -12521,11 +12533,11 @@
         <v>1081</v>
       </c>
       <c r="N330" t="str">
-        <f>"update lab set lab =  " &amp;C330&amp; " , country =  "&amp;H330&amp;"  where lab_id = "&amp;A330</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire , country =  33130154949  where lab_id = 330</v>
       </c>
     </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A331">
         <v>331</v>
       </c>
@@ -12545,11 +12557,11 @@
         <v>282</v>
       </c>
       <c r="N331" t="str">
-        <f>"update lab set lab =  " &amp;C331&amp; " , country =  "&amp;H331&amp;"  where lab_id = "&amp;A331</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Laboratoire des Etalons et des Intercomparaisons , country =    where lab_id = 331</v>
       </c>
     </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A332">
         <v>332</v>
       </c>
@@ -12578,11 +12590,11 @@
         <v>1090</v>
       </c>
       <c r="N332" t="str">
-        <f>"update lab set lab =  " &amp;C332&amp; " , country =  "&amp;H332&amp;"  where lab_id = "&amp;A332</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Federal Maritime and Hydrographic Agency , country =  494031903300  where lab_id = 332</v>
       </c>
     </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A333">
         <v>333</v>
       </c>
@@ -12608,11 +12620,11 @@
         <v>1094</v>
       </c>
       <c r="N333" t="str">
-        <f>"update lab set lab =  " &amp;C333&amp; " , country =  "&amp;H333&amp;"  where lab_id = "&amp;A333</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Radiological Protection Institute of Ireland , country =    where lab_id = 333</v>
       </c>
     </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A334">
         <v>334</v>
       </c>
@@ -12638,11 +12650,11 @@
         <v>1098</v>
       </c>
       <c r="N334" t="str">
-        <f>"update lab set lab =  " &amp;C334&amp; " , country =  "&amp;H334&amp;"  where lab_id = "&amp;A334</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  University College Dublin Department of Experimental Physics , country =    where lab_id = 334</v>
       </c>
     </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A335">
         <v>335</v>
       </c>
@@ -12677,11 +12689,11 @@
         <v>1104</v>
       </c>
       <c r="N335" t="str">
-        <f>"update lab set lab =  " &amp;C335&amp; " , country =  "&amp;H335&amp;"  where lab_id = "&amp;A335</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Norwegian Radiation Protection Authority _NRPA_ , country =  4767162535  where lab_id = 335</v>
       </c>
     </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A336">
         <v>336</v>
       </c>
@@ -12704,11 +12716,11 @@
         <v>1109</v>
       </c>
       <c r="N336" t="str">
-        <f>"update lab set lab =  " &amp;C336&amp; " , country =  "&amp;H336&amp;"  where lab_id = "&amp;A336</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Instituto Tecnológico e Nuclear , country =  351 21 9946317  where lab_id = 336</v>
       </c>
     </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A337">
         <v>337</v>
       </c>
@@ -12740,11 +12752,11 @@
         <v>1116</v>
       </c>
       <c r="N337" t="str">
-        <f>"update lab set lab =  " &amp;C337&amp; " , country =  "&amp;H337&amp;"  where lab_id = "&amp;A337</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Coordinadora del Programa Científico Técnico , country =  34 913357217  where lab_id = 337</v>
       </c>
     </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A338">
         <v>338</v>
       </c>
@@ -12767,11 +12779,11 @@
         <v>1120</v>
       </c>
       <c r="N338" t="str">
-        <f>"update lab set lab =  " &amp;C338&amp; " , country =  "&amp;H338&amp;"  where lab_id = "&amp;A338</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Swedish Radiation Protection Authority , country =    where lab_id = 338</v>
       </c>
     </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A339">
         <v>339</v>
       </c>
@@ -12800,11 +12812,11 @@
         <v>1127</v>
       </c>
       <c r="N339" t="str">
-        <f>"update lab set lab =  " &amp;C339&amp; " , country =  "&amp;H339&amp;"  where lab_id = "&amp;A339</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Cefas Lowestoft Laboratory , country =  01502 524477  where lab_id = 339</v>
       </c>
     </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A340">
         <v>340</v>
       </c>
@@ -12833,11 +12845,11 @@
         <v>1132</v>
       </c>
       <c r="N340" t="str">
-        <f>"update lab set lab =  " &amp;C340&amp; " , country =  "&amp;H340&amp;"  where lab_id = "&amp;A340</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  SVERIGE S  STRÅL SÄKERHETS MYNDIGHETEN , country =  +46 8 799 40 00  where lab_id = 340</v>
       </c>
     </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A341">
         <v>341</v>
       </c>
@@ -12866,11 +12878,11 @@
         <v>1138</v>
       </c>
       <c r="N341" t="str">
-        <f>"update lab set lab =  " &amp;C341&amp; " , country =  "&amp;H341&amp;"  where lab_id = "&amp;A341</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  BUNDESFORSCHUNGANSTALT FÜR FISCHEREI , country =  _0 40_ 38 9050  where lab_id = 341</v>
       </c>
     </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A342">
         <v>342</v>
       </c>
@@ -12902,11 +12914,11 @@
         <v>1146</v>
       </c>
       <c r="N342" t="str">
-        <f>"update lab set lab =  " &amp;C342&amp; " , country =  "&amp;H342&amp;"  where lab_id = "&amp;A342</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  JOHAN HEINRICH VON THÜNEN-INSTITUTE , country =  +49531-5961003  where lab_id = 342</v>
       </c>
     </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A343">
         <v>343</v>
       </c>
@@ -12929,11 +12941,11 @@
         <v>1151</v>
       </c>
       <c r="N343" t="str">
-        <f>"update lab set lab =  " &amp;C343&amp; " , country =  "&amp;H343&amp;"  where lab_id = "&amp;A343</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Meteorological Research Institute , country =    where lab_id = 343</v>
       </c>
     </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A344">
         <v>344</v>
       </c>
@@ -12956,11 +12968,11 @@
         <v>1156</v>
       </c>
       <c r="N344" t="str">
-        <f>"update lab set lab =  " &amp;C344&amp; " , country =  "&amp;H344&amp;"  where lab_id = "&amp;A344</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Research Institute for Global Change , country =    where lab_id = 344</v>
       </c>
     </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A345">
         <v>345</v>
       </c>
@@ -12986,11 +12998,11 @@
         <v>1161</v>
       </c>
       <c r="N345" t="str">
-        <f>"update lab set lab =  " &amp;C345&amp; " , country =  "&amp;H345&amp;"  where lab_id = "&amp;A345</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Laboratory of Ion Beam Physics _LIP_, ETZ Zürich, Switzerland , country =    where lab_id = 345</v>
       </c>
     </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A346">
         <v>346</v>
       </c>
@@ -13013,11 +13025,11 @@
         <v>505</v>
       </c>
       <c r="N346" t="str">
-        <f>"update lab set lab =  " &amp;C346&amp; " , country =  "&amp;H346&amp;"  where lab_id = "&amp;A346</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Marine Ecology Research Institute , country =    where lab_id = 346</v>
       </c>
     </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A347">
         <v>347</v>
       </c>
@@ -13040,11 +13052,11 @@
         <v>1171</v>
       </c>
       <c r="N347" t="str">
-        <f>"update lab set lab =  " &amp;C347&amp; " , country =  "&amp;H347&amp;"  where lab_id = "&amp;A347</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Fisheries Research Agency - Research Center for Fisheries Oceanography and Marine Ecosystem , country =    where lab_id = 347</v>
       </c>
     </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A348">
         <v>348</v>
       </c>
@@ -13067,11 +13079,11 @@
         <v>1174</v>
       </c>
       <c r="N348" t="str">
-        <f>"update lab set lab =  " &amp;C348&amp; " , country =  "&amp;H348&amp;"  where lab_id = "&amp;A348</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Institute of Biogeosciences , country =    where lab_id = 348</v>
       </c>
     </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A349">
         <v>349</v>
       </c>
@@ -13091,11 +13103,11 @@
         <v>1178</v>
       </c>
       <c r="N349" t="str">
-        <f>"update lab set lab =  " &amp;C349&amp; " , country =  "&amp;H349&amp;"  where lab_id = "&amp;A349</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Japan Atomic Energy Agency , country =    where lab_id = 349</v>
       </c>
     </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A350">
         <v>350</v>
       </c>
@@ -13127,11 +13139,11 @@
         <v>1184</v>
       </c>
       <c r="N350" t="str">
-        <f>"update lab set lab =  " &amp;C350&amp; " , country =  "&amp;H350&amp;"  where lab_id = "&amp;A350</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Radiation Safety Department, Environmental Board , country =  +372 664 4900  where lab_id = 350</v>
       </c>
     </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A351">
         <v>351</v>
       </c>
@@ -13142,11 +13154,11 @@
         <v>1071</v>
       </c>
       <c r="N351" t="str">
-        <f>"update lab set lab =  " &amp;C351&amp; " , country =  "&amp;H351&amp;"  where lab_id = "&amp;A351</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  DTU Nutech , country =    where lab_id = 351</v>
       </c>
     </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A352">
         <v>352</v>
       </c>
@@ -13157,11 +13169,11 @@
         <v>177</v>
       </c>
       <c r="N352" t="str">
-        <f>"update lab set lab =  " &amp;C352&amp; " , country =  "&amp;H352&amp;"  where lab_id = "&amp;A352</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  EA-Environment Agency , country =    where lab_id = 352</v>
       </c>
     </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A353">
         <v>353</v>
       </c>
@@ -13172,11 +13184,11 @@
         <v>478</v>
       </c>
       <c r="N353" t="str">
-        <f>"update lab set lab =  " &amp;C353&amp; " , country =  "&amp;H353&amp;"  where lab_id = "&amp;A353</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Environmental Protection Agency , country =    where lab_id = 353</v>
       </c>
     </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A354">
         <v>354</v>
       </c>
@@ -13187,11 +13199,11 @@
         <v>177</v>
       </c>
       <c r="N354" t="str">
-        <f>"update lab set lab =  " &amp;C354&amp; " , country =  "&amp;H354&amp;"  where lab_id = "&amp;A354</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  FSA-Food Standards Agency , country =    where lab_id = 354</v>
       </c>
     </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A355">
         <v>355</v>
       </c>
@@ -13202,11 +13214,11 @@
         <v>1190</v>
       </c>
       <c r="N355" t="str">
-        <f>"update lab set lab =  " &amp;C355&amp; " , country =  "&amp;H355&amp;"  where lab_id = "&amp;A355</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Icelandic Radiation Safety Authority , country =    where lab_id = 355</v>
       </c>
     </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A356">
         <v>356</v>
       </c>
@@ -13220,11 +13232,11 @@
         <v>282</v>
       </c>
       <c r="N356" t="str">
-        <f>"update lab set lab =  " &amp;C356&amp; " , country =  "&amp;H356&amp;"  where lab_id = "&amp;A356</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   LERFA , country =    where lab_id = 356</v>
       </c>
     </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A357">
         <v>357</v>
       </c>
@@ -13238,11 +13250,11 @@
         <v>282</v>
       </c>
       <c r="N357" t="str">
-        <f>"update lab set lab =  " &amp;C357&amp; " , country =  "&amp;H357&amp;"  where lab_id = "&amp;A357</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   LRC , country =    where lab_id = 357</v>
       </c>
     </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A358">
         <v>358</v>
       </c>
@@ -13256,11 +13268,11 @@
         <v>282</v>
       </c>
       <c r="N358" t="str">
-        <f>"update lab set lab =  " &amp;C358&amp; " , country =  "&amp;H358&amp;"  where lab_id = "&amp;A358</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   LRC -  LMRE , country =    where lab_id = 358</v>
       </c>
     </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A359">
         <v>359</v>
       </c>
@@ -13274,11 +13286,11 @@
         <v>282</v>
       </c>
       <c r="N359" t="str">
-        <f>"update lab set lab =  " &amp;C359&amp; " , country =  "&amp;H359&amp;"  where lab_id = "&amp;A359</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   LRC -  LS3E , country =    where lab_id = 359</v>
       </c>
     </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A360">
         <v>360</v>
       </c>
@@ -13292,11 +13304,11 @@
         <v>282</v>
       </c>
       <c r="N360" t="str">
-        <f>"update lab set lab =  " &amp;C360&amp; " , country =  "&amp;H360&amp;"  where lab_id = "&amp;A360</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   LRC -  LSE , country =    where lab_id = 360</v>
       </c>
     </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A361">
         <v>361</v>
       </c>
@@ -13310,11 +13322,11 @@
         <v>282</v>
       </c>
       <c r="N361" t="str">
-        <f>"update lab set lab =  " &amp;C361&amp; " , country =  "&amp;H361&amp;"  where lab_id = "&amp;A361</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   LS3E , country =    where lab_id = 361</v>
       </c>
     </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A362">
         <v>362</v>
       </c>
@@ -13328,11 +13340,11 @@
         <v>282</v>
       </c>
       <c r="N362" t="str">
-        <f>"update lab set lab =  " &amp;C362&amp; " , country =  "&amp;H362&amp;"  where lab_id = "&amp;A362</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   LSE , country =    where lab_id = 362</v>
       </c>
     </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A363">
         <v>363</v>
       </c>
@@ -13346,11 +13358,11 @@
         <v>282</v>
       </c>
       <c r="N363" t="str">
-        <f>"update lab set lab =  " &amp;C363&amp; " , country =  "&amp;H363&amp;"  where lab_id = "&amp;A363</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   LVRE , country =    where lab_id = 363</v>
       </c>
     </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A364">
         <v>364</v>
       </c>
@@ -13364,11 +13376,11 @@
         <v>282</v>
       </c>
       <c r="N364" t="str">
-        <f>"update lab set lab =  " &amp;C364&amp; " , country =  "&amp;H364&amp;"  where lab_id = "&amp;A364</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   OPRI , country =    where lab_id = 364</v>
       </c>
     </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A365">
         <v>365</v>
       </c>
@@ -13382,11 +13394,11 @@
         <v>282</v>
       </c>
       <c r="N365" t="str">
-        <f>"update lab set lab =  " &amp;C365&amp; " , country =  "&amp;H365&amp;"  where lab_id = "&amp;A365</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   OPRI-LVRE , country =    where lab_id = 365</v>
       </c>
     </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A366">
         <v>366</v>
       </c>
@@ -13397,11 +13409,11 @@
         <v>630</v>
       </c>
       <c r="N366" t="str">
-        <f>"update lab set lab =  " &amp;C366&amp; " , country =  "&amp;H366&amp;"  where lab_id = "&amp;A366</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Institute for Energy Technology , country =    where lab_id = 366</v>
       </c>
     </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A367">
         <v>367</v>
       </c>
@@ -13412,11 +13424,11 @@
         <v>630</v>
       </c>
       <c r="N367" t="str">
-        <f>"update lab set lab =  " &amp;C367&amp; " , country =  "&amp;H367&amp;"  where lab_id = "&amp;A367</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Institute for Energy Technology  -   Norwegian Radiation Protection Authority , country =    where lab_id = 367</v>
       </c>
     </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A368">
         <v>368</v>
       </c>
@@ -13436,11 +13448,11 @@
         <v>630</v>
       </c>
       <c r="N368" t="str">
-        <f>"update lab set lab =  " &amp;C368&amp; " , country =  "&amp;H368&amp;"  where lab_id = "&amp;A368</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Institute of Marine Research , country =    where lab_id = 368</v>
       </c>
     </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A369">
         <v>369</v>
       </c>
@@ -13451,11 +13463,11 @@
         <v>630</v>
       </c>
       <c r="N369" t="str">
-        <f>"update lab set lab =  " &amp;C369&amp; " , country =  "&amp;H369&amp;"  where lab_id = "&amp;A369</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Institute of Marine Research  -   Norwegian Radiation Protection Authority , country =    where lab_id = 369</v>
       </c>
     </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A370">
         <v>370</v>
       </c>
@@ -13466,11 +13478,11 @@
         <v>340</v>
       </c>
       <c r="N370" t="str">
-        <f>"update lab set lab =  " &amp;C370&amp; " , country =  "&amp;H370&amp;"  where lab_id = "&amp;A370</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Johann Heinrich von Thünen Institute _vTI_ , country =    where lab_id = 370</v>
       </c>
     </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A371">
         <v>371</v>
       </c>
@@ -13481,11 +13493,11 @@
         <v>177</v>
       </c>
       <c r="N371" t="str">
-        <f>"update lab set lab =  " &amp;C371&amp; " , country =  "&amp;H371&amp;"  where lab_id = "&amp;A371</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  NIEA-Northern Ireland Environment Agency , country =    where lab_id = 371</v>
       </c>
     </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A372">
         <v>372</v>
       </c>
@@ -13499,11 +13511,11 @@
         <v>630</v>
       </c>
       <c r="N372" t="str">
-        <f>"update lab set lab =  " &amp;C372&amp; " , country =  "&amp;H372&amp;"  where lab_id = "&amp;A372</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Norwegian Radiation Protection Authority , country =    where lab_id = 372</v>
       </c>
     </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A373">
         <v>373</v>
       </c>
@@ -13514,11 +13526,11 @@
         <v>86</v>
       </c>
       <c r="N373" t="str">
-        <f>"update lab set lab =  " &amp;C373&amp; " , country =  "&amp;H373&amp;"  where lab_id = "&amp;A373</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Nuclear Energy Research Centre , country =    where lab_id = 373</v>
       </c>
     </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A374">
         <v>374</v>
       </c>
@@ -13529,11 +13541,11 @@
         <v>765</v>
       </c>
       <c r="N374" t="str">
-        <f>"update lab set lab =  " &amp;C374&amp; " , country =  "&amp;H374&amp;"  where lab_id = "&amp;A374</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Nuclear Safety Council , country =    where lab_id = 374</v>
       </c>
     </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A375">
         <v>376</v>
       </c>
@@ -13544,11 +13556,11 @@
         <v>589</v>
       </c>
       <c r="N375" t="str">
-        <f>"update lab set lab =  " &amp;C375&amp; " , country =  "&amp;H375&amp;"  where lab_id = "&amp;A375</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Rijkswaterstaat Centre for Water Management , country =    where lab_id = 376</v>
       </c>
     </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A376">
         <v>377</v>
       </c>
@@ -13559,11 +13571,11 @@
         <v>589</v>
       </c>
       <c r="N376" t="str">
-        <f>"update lab set lab =  " &amp;C376&amp; " , country =  "&amp;H376&amp;"  where lab_id = "&amp;A376</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Rijkswaterstaat Laboratory CIV , country =    where lab_id = 377</v>
       </c>
     </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A377">
         <v>378</v>
       </c>
@@ -13574,11 +13586,11 @@
         <v>86</v>
       </c>
       <c r="N377" t="str">
-        <f>"update lab set lab =  " &amp;C377&amp; " , country =  "&amp;H377&amp;"  where lab_id = "&amp;A377</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Scientific Institute of Public Health , country =    where lab_id = 378</v>
       </c>
     </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A378">
         <v>379</v>
       </c>
@@ -13589,11 +13601,11 @@
         <v>86</v>
       </c>
       <c r="N378" t="str">
-        <f>"update lab set lab =  " &amp;C378&amp; " , country =  "&amp;H378&amp;"  where lab_id = "&amp;A378</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  SCK  CEN , country =    where lab_id = 379</v>
       </c>
     </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A379">
         <v>380</v>
       </c>
@@ -13604,11 +13616,11 @@
         <v>177</v>
       </c>
       <c r="N379" t="str">
-        <f>"update lab set lab =  " &amp;C379&amp; " , country =  "&amp;H379&amp;"  where lab_id = "&amp;A379</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  SEPA-Scottish Environment Protection Agency , country =    where lab_id = 380</v>
       </c>
     </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A380">
         <v>381</v>
       </c>
@@ -13619,11 +13631,11 @@
         <v>99</v>
       </c>
       <c r="N380" t="str">
-        <f>"update lab set lab =  " &amp;C380&amp; " , country =  "&amp;H380&amp;"  where lab_id = "&amp;A380</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Swedish Radiation Safety Authority , country =    where lab_id = 381</v>
       </c>
     </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A381">
         <v>382</v>
       </c>
@@ -13634,11 +13646,11 @@
         <v>630</v>
       </c>
       <c r="N381" t="str">
-        <f>"update lab set lab =  " &amp;C381&amp; " , country =  "&amp;H381&amp;"  where lab_id = "&amp;A381</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  The Norwegian Food Control Authority , country =    where lab_id = 382</v>
       </c>
     </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A382">
         <v>383</v>
       </c>
@@ -13649,11 +13661,11 @@
         <v>177</v>
       </c>
       <c r="N382" t="str">
-        <f>"update lab set lab =  " &amp;C382&amp; " , country =  "&amp;H382&amp;"  where lab_id = "&amp;A382</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  BEIS _formerly DECC_ , country =    where lab_id = 383</v>
       </c>
     </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A383">
         <v>384</v>
       </c>
@@ -13664,11 +13676,11 @@
         <v>177</v>
       </c>
       <c r="N383" t="str">
-        <f>"update lab set lab =  " &amp;C383&amp; " , country =  "&amp;H383&amp;"  where lab_id = "&amp;A383</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Corystes 14 -  2004 , country =    where lab_id = 384</v>
       </c>
     </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A384">
         <v>385</v>
       </c>
@@ -13679,11 +13691,11 @@
         <v>177</v>
       </c>
       <c r="N384" t="str">
-        <f>"update lab set lab =  " &amp;C384&amp; " , country =  "&amp;H384&amp;"  where lab_id = "&amp;A384</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Defra-Department for Environment,  Food and Rural Affairs , country =    where lab_id = 385</v>
       </c>
     </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A385">
         <v>386</v>
       </c>
@@ -13694,11 +13706,11 @@
         <v>177</v>
       </c>
       <c r="N385" t="str">
-        <f>"update lab set lab =  " &amp;C385&amp; " , country =  "&amp;H385&amp;"  where lab_id = "&amp;A385</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Endeavour 10 -  2004 , country =    where lab_id = 386</v>
       </c>
     </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A386">
         <v>387</v>
       </c>
@@ -13709,11 +13721,11 @@
         <v>340</v>
       </c>
       <c r="N386" t="str">
-        <f>"update lab set lab =  " &amp;C386&amp; " , country =  "&amp;H386&amp;"  where lab_id = "&amp;A386</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Federal Maritime and Hydrographic Agency, Hamburg , country =    where lab_id = 387</v>
       </c>
     </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A387">
         <v>388</v>
       </c>
@@ -13727,11 +13739,11 @@
         <v>282</v>
       </c>
       <c r="N387" t="str">
-        <f>"update lab set lab =  " &amp;C387&amp; " , country =  "&amp;H387&amp;"  where lab_id = "&amp;A387</f>
+        <f t="shared" si="5"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   LRC -  LS3E, LTE , country =    where lab_id = 388</v>
       </c>
     </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A388">
         <v>389</v>
       </c>
@@ -13745,11 +13757,11 @@
         <v>282</v>
       </c>
       <c r="N388" t="str">
-        <f>"update lab set lab =  " &amp;C388&amp; " , country =  "&amp;H388&amp;"  where lab_id = "&amp;A388</f>
+        <f t="shared" ref="N388:N451" si="6">"update lab set lab =  " &amp;C388&amp; " , country =  "&amp;H388&amp;"  where lab_id = "&amp;A388</f>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   LRC -  LS3E -  LMN , country =    where lab_id = 389</v>
       </c>
     </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A389">
         <v>390</v>
       </c>
@@ -13763,11 +13775,11 @@
         <v>282</v>
       </c>
       <c r="N389" t="str">
-        <f>"update lab set lab =  " &amp;C389&amp; " , country =  "&amp;H389&amp;"  where lab_id = "&amp;A389</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   LRC -  LS3E -  RSMASS , country =    where lab_id = 390</v>
       </c>
     </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A390">
         <v>391</v>
       </c>
@@ -13781,11 +13793,11 @@
         <v>282</v>
       </c>
       <c r="N390" t="str">
-        <f>"update lab set lab =  " &amp;C390&amp; " , country =  "&amp;H390&amp;"  where lab_id = "&amp;A390</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   LRC -  LSE -  LMN , country =    where lab_id = 391</v>
       </c>
     </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A391">
         <v>392</v>
       </c>
@@ -13799,11 +13811,11 @@
         <v>282</v>
       </c>
       <c r="N391" t="str">
-        <f>"update lab set lab =  " &amp;C391&amp; " , country =  "&amp;H391&amp;"  where lab_id = "&amp;A391</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   LRC -  LTE, LMN , country =    where lab_id = 392</v>
       </c>
     </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A392">
         <v>393</v>
       </c>
@@ -13817,11 +13829,11 @@
         <v>282</v>
       </c>
       <c r="N392" t="str">
-        <f>"update lab set lab =  " &amp;C392&amp; " , country =  "&amp;H392&amp;"  where lab_id = "&amp;A392</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   LS3E -  Marine Nationale , country =    where lab_id = 393</v>
       </c>
     </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A393">
         <v>394</v>
       </c>
@@ -13835,11 +13847,11 @@
         <v>282</v>
       </c>
       <c r="N393" t="str">
-        <f>"update lab set lab =  " &amp;C393&amp; " , country =  "&amp;H393&amp;"  where lab_id = "&amp;A393</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   LS3E -  RSMASS , country =    where lab_id = 394</v>
       </c>
     </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A394">
         <v>395</v>
       </c>
@@ -13853,11 +13865,11 @@
         <v>282</v>
       </c>
       <c r="N394" t="str">
-        <f>"update lab set lab =  " &amp;C394&amp; " , country =  "&amp;H394&amp;"  where lab_id = "&amp;A394</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   LSE -  Marine Nationale , country =    where lab_id = 395</v>
       </c>
     </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A395">
         <v>396</v>
       </c>
@@ -13871,11 +13883,11 @@
         <v>282</v>
       </c>
       <c r="N395" t="str">
-        <f>"update lab set lab =  " &amp;C395&amp; " , country =  "&amp;H395&amp;"  where lab_id = "&amp;A395</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   LVRE -  MN , country =    where lab_id = 396</v>
       </c>
     </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A396">
         <v>397</v>
       </c>
@@ -13889,11 +13901,11 @@
         <v>282</v>
       </c>
       <c r="N396" t="str">
-        <f>"update lab set lab =  " &amp;C396&amp; " , country =  "&amp;H396&amp;"  where lab_id = "&amp;A396</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   LVRE -  RSMASS , country =    where lab_id = 397</v>
       </c>
     </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A397">
         <v>398</v>
       </c>
@@ -13907,11 +13919,11 @@
         <v>282</v>
       </c>
       <c r="N397" t="str">
-        <f>"update lab set lab =  " &amp;C397&amp; " , country =  "&amp;H397&amp;"  where lab_id = "&amp;A397</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   OPRI-LVRE -  MN , country =    where lab_id = 398</v>
       </c>
     </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A398">
         <v>399</v>
       </c>
@@ -13925,11 +13937,11 @@
         <v>282</v>
       </c>
       <c r="N398" t="str">
-        <f>"update lab set lab =  " &amp;C398&amp; " , country =  "&amp;H398&amp;"  where lab_id = "&amp;A398</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   OPRI -  DDASS , country =    where lab_id = 399</v>
       </c>
     </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A399">
         <v>400</v>
       </c>
@@ -13943,11 +13955,11 @@
         <v>282</v>
       </c>
       <c r="N399" t="str">
-        <f>"update lab set lab =  " &amp;C399&amp; " , country =  "&amp;H399&amp;"  where lab_id = "&amp;A399</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   OPRI -  MN , country =    where lab_id = 400</v>
       </c>
     </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A400">
         <v>401</v>
       </c>
@@ -13961,11 +13973,11 @@
         <v>282</v>
       </c>
       <c r="N400" t="str">
-        <f>"update lab set lab =  " &amp;C400&amp; " , country =  "&amp;H400&amp;"  where lab_id = "&amp;A400</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire - LS3E -  STEME _ALOKA_ , country =    where lab_id = 401</v>
       </c>
     </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A401">
         <v>402</v>
       </c>
@@ -13979,11 +13991,11 @@
         <v>282</v>
       </c>
       <c r="N401" t="str">
-        <f>"update lab set lab =  " &amp;C401&amp; " , country =  "&amp;H401&amp;"  where lab_id = "&amp;A401</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire - LSE -  STEME _ALOKA_ , country =    where lab_id = 402</v>
       </c>
     </row>
-    <row r="402" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A402">
         <v>403</v>
       </c>
@@ -14003,11 +14015,11 @@
         <v>505</v>
       </c>
       <c r="N402" t="str">
-        <f>"update lab set lab =  " &amp;C402&amp; " , country =  "&amp;H402&amp;"  where lab_id = "&amp;A402</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  The Central Research Institute of Electric Power Industry , country =    where lab_id = 403</v>
       </c>
     </row>
-    <row r="403" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A403">
         <v>404</v>
       </c>
@@ -14024,11 +14036,11 @@
         <v>31</v>
       </c>
       <c r="N403" t="str">
-        <f>"update lab set lab =  " &amp;C403&amp; " , country =  "&amp;H403&amp;"  where lab_id = "&amp;A403</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Polish Academy of Sciences - Institute of Nuclear Physics , country =    where lab_id = 404</v>
       </c>
     </row>
-    <row r="404" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A404">
         <v>405</v>
       </c>
@@ -14042,11 +14054,11 @@
         <v>48</v>
       </c>
       <c r="N404" t="str">
-        <f>"update lab set lab =  " &amp;C404&amp; " , country =  "&amp;H404&amp;"  where lab_id = "&amp;A404</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  University of Miami , country =    where lab_id = 405</v>
       </c>
     </row>
-    <row r="405" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A405">
         <v>406</v>
       </c>
@@ -14060,11 +14072,11 @@
         <v>48</v>
       </c>
       <c r="N405" t="str">
-        <f>"update lab set lab =  " &amp;C405&amp; " , country =  "&amp;H405&amp;"  where lab_id = "&amp;A405</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  University of Washington , country =    where lab_id = 406</v>
       </c>
     </row>
-    <row r="406" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A406">
         <v>407</v>
       </c>
@@ -14084,11 +14096,11 @@
         <v>48</v>
       </c>
       <c r="N406" t="str">
-        <f>"update lab set lab =  " &amp;C406&amp; " , country =  "&amp;H406&amp;"  where lab_id = "&amp;A406</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Scripps Institution of Oceanography , country =    where lab_id = 407</v>
       </c>
     </row>
-    <row r="407" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A407">
         <v>408</v>
       </c>
@@ -14102,11 +14114,11 @@
         <v>48</v>
       </c>
       <c r="N407" t="str">
-        <f>"update lab set lab =  " &amp;C407&amp; " , country =  "&amp;H407&amp;"  where lab_id = "&amp;A407</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  University of Southern California , country =    where lab_id = 408</v>
       </c>
     </row>
-    <row r="408" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A408">
         <v>409</v>
       </c>
@@ -14126,11 +14138,11 @@
         <v>48</v>
       </c>
       <c r="N408" t="str">
-        <f>"update lab set lab =  " &amp;C408&amp; " , country =  "&amp;H408&amp;"  where lab_id = "&amp;A408</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Yale University , country =    where lab_id = 409</v>
       </c>
     </row>
-    <row r="409" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A409">
         <v>410</v>
       </c>
@@ -14147,11 +14159,11 @@
         <v>128</v>
       </c>
       <c r="N409" t="str">
-        <f>"update lab set lab =  " &amp;C409&amp; " , country =  "&amp;H409&amp;"  where lab_id = "&amp;A409</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Radiation Protection Bureau, Health Canada , country =    where lab_id = 410</v>
       </c>
     </row>
-    <row r="410" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A410">
         <v>411</v>
       </c>
@@ -14171,11 +14183,11 @@
         <v>128</v>
       </c>
       <c r="N410" t="str">
-        <f>"update lab set lab =  " &amp;C410&amp; " , country =  "&amp;H410&amp;"  where lab_id = "&amp;A410</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Fisheries and Oceans Canada , country =    where lab_id = 411</v>
       </c>
     </row>
-    <row r="411" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A411">
         <v>412</v>
       </c>
@@ -14192,11 +14204,11 @@
         <v>282</v>
       </c>
       <c r="N411" t="str">
-        <f>"update lab set lab =  " &amp;C411&amp; " , country =  "&amp;H411&amp;"  where lab_id = "&amp;A411</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Orano _former Areva_ NC La Hague , country =    where lab_id = 412</v>
       </c>
     </row>
-    <row r="412" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A412">
         <v>413</v>
       </c>
@@ -14216,11 +14228,11 @@
         <v>282</v>
       </c>
       <c r="N412" t="str">
-        <f>"update lab set lab =  " &amp;C412&amp; " , country =  "&amp;H412&amp;"  where lab_id = "&amp;A412</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Association pour le Contrôle de la Radioactivité dans l Ouest , country =    where lab_id = 413</v>
       </c>
     </row>
-    <row r="413" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A413">
         <v>414</v>
       </c>
@@ -14240,11 +14252,11 @@
         <v>282</v>
       </c>
       <c r="N413" t="str">
-        <f>"update lab set lab =  " &amp;C413&amp; " , country =  "&amp;H413&amp;"  where lab_id = "&amp;A413</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Base navale - Laboratoire de Surveillance Radiologique _LSR_ - Brest , country =    where lab_id = 414</v>
       </c>
     </row>
-    <row r="414" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A414">
         <v>415</v>
       </c>
@@ -14264,11 +14276,11 @@
         <v>282</v>
       </c>
       <c r="N414" t="str">
-        <f>"update lab set lab =  " &amp;C414&amp; " , country =  "&amp;H414&amp;"  where lab_id = "&amp;A414</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Base navale - Laboratoire de Surveillance Radiologique _LSR_ - Cherbourg , country =    where lab_id = 415</v>
       </c>
     </row>
-    <row r="415" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A415">
         <v>416</v>
       </c>
@@ -14288,11 +14300,11 @@
         <v>282</v>
       </c>
       <c r="N415" t="str">
-        <f>"update lab set lab =  " &amp;C415&amp; " , country =  "&amp;H415&amp;"  where lab_id = "&amp;A415</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Base navale - Service de Protection Radiologique - Ile longue , country =    where lab_id = 416</v>
       </c>
     </row>
-    <row r="416" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A416">
         <v>417</v>
       </c>
@@ -14312,11 +14324,11 @@
         <v>282</v>
       </c>
       <c r="N416" t="str">
-        <f>"update lab set lab =  " &amp;C416&amp; " , country =  "&amp;H416&amp;"  where lab_id = "&amp;A416</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Commission Locale d Information _CLI_ de Gravelines , country =    where lab_id = 417</v>
       </c>
     </row>
-    <row r="417" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A417">
         <v>418</v>
       </c>
@@ -14336,11 +14348,11 @@
         <v>282</v>
       </c>
       <c r="N417" t="str">
-        <f>"update lab set lab =  " &amp;C417&amp; " , country =  "&amp;H417&amp;"  where lab_id = "&amp;A417</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Orano _former Areva_ Malvési , country =    where lab_id = 418</v>
       </c>
     </row>
-    <row r="418" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A418">
         <v>419</v>
       </c>
@@ -14360,11 +14372,11 @@
         <v>282</v>
       </c>
       <c r="N418" t="str">
-        <f>"update lab set lab =  " &amp;C418&amp; " , country =  "&amp;H418&amp;"  where lab_id = "&amp;A418</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  EDF - Centre Nucléaire de Production d Électricite de Flamanville , country =    where lab_id = 419</v>
       </c>
     </row>
-    <row r="419" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A419">
         <v>420</v>
       </c>
@@ -14387,11 +14399,11 @@
         <v>282</v>
       </c>
       <c r="N419" t="str">
-        <f>"update lab set lab =  " &amp;C419&amp; " , country =  "&amp;H419&amp;"  where lab_id = "&amp;A419</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  EDF - Centre Nucléaire de Production d Électricite de Paluel , country =    where lab_id = 420</v>
       </c>
     </row>
-    <row r="420" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A420">
         <v>421</v>
       </c>
@@ -14411,11 +14423,11 @@
         <v>282</v>
       </c>
       <c r="N420" t="str">
-        <f>"update lab set lab =  " &amp;C420&amp; " , country =  "&amp;H420&amp;"  where lab_id = "&amp;A420</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  EDF - Centre Nucléaire de Production d Électricite de Penly , country =    where lab_id = 421</v>
       </c>
     </row>
-    <row r="421" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A421">
         <v>422</v>
       </c>
@@ -14429,11 +14441,11 @@
         <v>282</v>
       </c>
       <c r="N421" t="str">
-        <f>"update lab set lab =  " &amp;C421&amp; " , country =  "&amp;H421&amp;"  where lab_id = "&amp;A421</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  EDF - Centre Nucléaire de Production d Électricite de Blayais , country =    where lab_id = 422</v>
       </c>
     </row>
-    <row r="422" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A422">
         <v>423</v>
       </c>
@@ -14447,11 +14459,11 @@
         <v>282</v>
       </c>
       <c r="N422" t="str">
-        <f>"update lab set lab =  " &amp;C422&amp; " , country =  "&amp;H422&amp;"  where lab_id = "&amp;A422</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  EDF - Centre Nucléaire de Production d Électricite de Gravelines , country =    where lab_id = 423</v>
       </c>
     </row>
-    <row r="423" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A423">
         <v>424</v>
       </c>
@@ -14468,11 +14480,11 @@
         <v>86</v>
       </c>
       <c r="N423" t="str">
-        <f>"update lab set lab =  " &amp;C423&amp; " , country =  "&amp;H423&amp;"  where lab_id = "&amp;A423</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  FBFC International , country =    where lab_id = 424</v>
       </c>
     </row>
-    <row r="424" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A424">
         <v>425</v>
       </c>
@@ -14489,11 +14501,11 @@
         <v>282</v>
       </c>
       <c r="N424" t="str">
-        <f>"update lab set lab =  " &amp;C424&amp; " , country =  "&amp;H424&amp;"  where lab_id = "&amp;A424</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Orano _former Areva_ Tricastin Réseau de Surveillance de l Environnement _RSE_ , country =    where lab_id = 425</v>
       </c>
     </row>
-    <row r="425" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A425">
         <v>426</v>
       </c>
@@ -14513,11 +14525,11 @@
         <v>1267</v>
       </c>
       <c r="N425" t="str">
-        <f>"update lab set lab =  " &amp;C425&amp; " , country =  "&amp;H425&amp;"  where lab_id = "&amp;A425</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Commission Locale d Information Nucléaire _CLIN_ du Blayais , country =  +33 5 56 99 51 20  where lab_id = 426</v>
       </c>
     </row>
-    <row r="426" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A426">
         <v>427</v>
       </c>
@@ -14534,11 +14546,11 @@
         <v>282</v>
       </c>
       <c r="N426" t="str">
-        <f>"update lab set lab =  " &amp;C426&amp; " , country =  "&amp;H426&amp;"  where lab_id = "&amp;A426</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Institut Laue-Langevin , country =    where lab_id = 427</v>
       </c>
     </row>
-    <row r="427" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A427">
         <v>428</v>
       </c>
@@ -14555,11 +14567,11 @@
         <v>282</v>
       </c>
       <c r="N427" t="str">
-        <f>"update lab set lab =  " &amp;C427&amp; " , country =  "&amp;H427&amp;"  where lab_id = "&amp;A427</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  LABEO Manche , country =    where lab_id = 428</v>
       </c>
     </row>
-    <row r="428" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A428">
         <v>429</v>
       </c>
@@ -14579,11 +14591,11 @@
         <v>282</v>
       </c>
       <c r="N428" t="str">
-        <f>"update lab set lab =  " &amp;C428&amp; " , country =  "&amp;H428&amp;"  where lab_id = "&amp;A428</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Autorité de Sûreté Nucléaire _ASN_ , country =    where lab_id = 429</v>
       </c>
     </row>
-    <row r="429" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A429">
         <v>430</v>
       </c>
@@ -14606,11 +14618,11 @@
         <v>1280</v>
       </c>
       <c r="N429" t="str">
-        <f>"update lab set lab =  " &amp;C429&amp; " , country =  "&amp;H429&amp;"  where lab_id = "&amp;A429</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Commissariat à l énergie atomique et aux énergies alternatives - Paris-Saclay , country =  +33 1 69 08 60 00  where lab_id = 430</v>
       </c>
     </row>
-    <row r="430" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A430">
         <v>431</v>
       </c>
@@ -14630,11 +14642,11 @@
         <v>48</v>
       </c>
       <c r="N430" t="str">
-        <f>"update lab set lab =  " &amp;C430&amp; " , country =  "&amp;H430&amp;"  where lab_id = "&amp;A430</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  National Oceanic and Atmospheric Administration _NOAA_ , country =    where lab_id = 431</v>
       </c>
     </row>
-    <row r="431" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A431">
         <v>432</v>
       </c>
@@ -14654,11 +14666,11 @@
         <v>1286</v>
       </c>
       <c r="N431" t="str">
-        <f>"update lab set lab =  " &amp;C431&amp; " , country =  "&amp;H431&amp;"  where lab_id = "&amp;A431</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Qatar University , country =    where lab_id = 432</v>
       </c>
     </row>
-    <row r="432" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A432">
         <v>433</v>
       </c>
@@ -14675,11 +14687,11 @@
         <v>48</v>
       </c>
       <c r="N432" t="str">
-        <f>"update lab set lab =  " &amp;C432&amp; " , country =  "&amp;H432&amp;"  where lab_id = "&amp;A432</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  University of Hawaii , country =    where lab_id = 433</v>
       </c>
     </row>
-    <row r="433" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A433">
         <v>434</v>
       </c>
@@ -14696,11 +14708,11 @@
         <v>478</v>
       </c>
       <c r="N433" t="str">
-        <f>"update lab set lab =  " &amp;C433&amp; " , country =  "&amp;H433&amp;"  where lab_id = "&amp;A433</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  University College Cork , country =    where lab_id = 434</v>
       </c>
     </row>
-    <row r="434" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A434">
         <v>435</v>
       </c>
@@ -14717,11 +14729,11 @@
         <v>48</v>
       </c>
       <c r="N434" t="str">
-        <f>"update lab set lab =  " &amp;C434&amp; " , country =  "&amp;H434&amp;"  where lab_id = "&amp;A434</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Rutgers University , country =    where lab_id = 435</v>
       </c>
     </row>
-    <row r="435" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A435">
         <v>436</v>
       </c>
@@ -14741,11 +14753,11 @@
         <v>485</v>
       </c>
       <c r="N435" t="str">
-        <f>"update lab set lab =  " &amp;C435&amp; " , country =  "&amp;H435&amp;"  where lab_id = "&amp;A435</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Ispettorato Nazionale per la Sicurezza Nucleare e la Radioprotezione , country =    where lab_id = 436</v>
       </c>
     </row>
-    <row r="436" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A436">
         <v>437</v>
       </c>
@@ -14762,11 +14774,11 @@
         <v>622</v>
       </c>
       <c r="N436" t="str">
-        <f>"update lab set lab =  " &amp;C436&amp; " , country =  "&amp;H436&amp;"  where lab_id = "&amp;A436</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  University of Canterbury , country =    where lab_id = 437</v>
       </c>
     </row>
-    <row r="437" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A437">
         <v>438</v>
       </c>
@@ -14783,11 +14795,11 @@
         <v>340</v>
       </c>
       <c r="N437" t="str">
-        <f>"update lab set lab =  " &amp;C437&amp; " , country =  "&amp;H437&amp;"  where lab_id = "&amp;A437</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Thünen Institute of Fisheries Ecology , country =    where lab_id = 438</v>
       </c>
     </row>
-    <row r="438" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A438">
         <v>439</v>
       </c>
@@ -14804,11 +14816,11 @@
         <v>451</v>
       </c>
       <c r="N438" t="str">
-        <f>"update lab set lab =  " &amp;C438&amp; " , country =  "&amp;H438&amp;"  where lab_id = "&amp;A438</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  C. Abdul Hakeem College , country =    where lab_id = 439</v>
       </c>
     </row>
-    <row r="439" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A439">
         <v>440</v>
       </c>
@@ -14828,11 +14840,11 @@
         <v>48</v>
       </c>
       <c r="N439" t="str">
-        <f>"update lab set lab =  " &amp;C439&amp; " , country =  "&amp;H439&amp;"  where lab_id = "&amp;A439</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  U.S. Department of Energy , country =    where lab_id = 440</v>
       </c>
     </row>
-    <row r="440" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A440">
         <v>441</v>
       </c>
@@ -14849,11 +14861,11 @@
         <v>537</v>
       </c>
       <c r="N440" t="str">
-        <f>"update lab set lab =  " &amp;C440&amp; " , country =  "&amp;H440&amp;"  where lab_id = "&amp;A440</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Seoul National University , country =    where lab_id = 441</v>
       </c>
     </row>
-    <row r="441" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A441">
         <v>442</v>
       </c>
@@ -14870,11 +14882,11 @@
         <v>48</v>
       </c>
       <c r="N441" t="str">
-        <f>"update lab set lab =  " &amp;C441&amp; " , country =  "&amp;H441&amp;"  where lab_id = "&amp;A441</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Los Alamos National Laboratory , country =    where lab_id = 442</v>
       </c>
     </row>
-    <row r="442" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A442">
         <v>443</v>
       </c>
@@ -14891,11 +14903,11 @@
         <v>42</v>
       </c>
       <c r="N442" t="str">
-        <f>"update lab set lab =  " &amp;C442&amp; " , country =  "&amp;H442&amp;"  where lab_id = "&amp;A442</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  University of Melbourne , country =    where lab_id = 443</v>
       </c>
     </row>
-    <row r="443" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A443">
         <v>444</v>
       </c>
@@ -14912,11 +14924,11 @@
         <v>48</v>
       </c>
       <c r="N443" t="str">
-        <f>"update lab set lab =  " &amp;C443&amp; " , country =  "&amp;H443&amp;"  where lab_id = "&amp;A443</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Brookhaven National Laboratory , country =    where lab_id = 444</v>
       </c>
     </row>
-    <row r="444" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A444">
         <v>445</v>
       </c>
@@ -14933,11 +14945,11 @@
         <v>505</v>
       </c>
       <c r="N444" t="str">
-        <f>"update lab set lab =  " &amp;C444&amp; " , country =  "&amp;H444&amp;"  where lab_id = "&amp;A444</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Hokkaido Pharmaceutical Association Public Health Examination Center , country =    where lab_id = 445</v>
       </c>
     </row>
-    <row r="445" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A445">
         <v>446</v>
       </c>
@@ -14957,11 +14969,11 @@
         <v>752</v>
       </c>
       <c r="N445" t="str">
-        <f>"update lab set lab =  " &amp;C445&amp; " , country =  "&amp;H445&amp;"  where lab_id = "&amp;A445</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  University of Cape Town , country =    where lab_id = 446</v>
       </c>
     </row>
-    <row r="446" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A446">
         <v>447</v>
       </c>
@@ -14981,11 +14993,11 @@
         <v>340</v>
       </c>
       <c r="N446" t="str">
-        <f>"update lab set lab =  " &amp;C446&amp; " , country =  "&amp;H446&amp;"  where lab_id = "&amp;A446</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Leibniz Center for Tropical Marine Ecology , country =    where lab_id = 447</v>
       </c>
     </row>
-    <row r="447" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A447">
         <v>448</v>
       </c>
@@ -15005,11 +15017,11 @@
         <v>109</v>
       </c>
       <c r="N447" t="str">
-        <f>"update lab set lab =  " &amp;C447&amp; " , country =  "&amp;H447&amp;"  where lab_id = "&amp;A447</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Universidade Federal Fluminense , country =    where lab_id = 448</v>
       </c>
     </row>
-    <row r="448" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A448">
         <v>449</v>
       </c>
@@ -15029,11 +15041,11 @@
         <v>48</v>
       </c>
       <c r="N448" t="str">
-        <f>"update lab set lab =  " &amp;C448&amp; " , country =  "&amp;H448&amp;"  where lab_id = "&amp;A448</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  University of California , country =    where lab_id = 449</v>
       </c>
     </row>
-    <row r="449" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A449">
         <v>450</v>
       </c>
@@ -15050,11 +15062,11 @@
         <v>856</v>
       </c>
       <c r="N449" t="str">
-        <f>"update lab set lab =  " &amp;C449&amp; " , country =  "&amp;H449&amp;"  where lab_id = "&amp;A449</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Istanbul University , country =    where lab_id = 450</v>
       </c>
     </row>
-    <row r="450" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A450">
         <v>451</v>
       </c>
@@ -15074,11 +15086,11 @@
         <v>451</v>
       </c>
       <c r="N450" t="str">
-        <f>"update lab set lab =  " &amp;C450&amp; " , country =  "&amp;H450&amp;"  where lab_id = "&amp;A450</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  Bhabha Atomic Research Center , country =    where lab_id = 451</v>
       </c>
     </row>
-    <row r="451" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A451">
         <v>452</v>
       </c>
@@ -15095,11 +15107,11 @@
         <v>735</v>
       </c>
       <c r="N451" t="str">
-        <f>"update lab set lab =  " &amp;C451&amp; " , country =  "&amp;H451&amp;"  where lab_id = "&amp;A451</f>
+        <f t="shared" si="6"/>
         <v>update lab set lab =  King Saud University , country =    where lab_id = 452</v>
       </c>
     </row>
-    <row r="452" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A452">
         <v>453</v>
       </c>
@@ -15119,11 +15131,11 @@
         <v>505</v>
       </c>
       <c r="N452" t="str">
-        <f>"update lab set lab =  " &amp;C452&amp; " , country =  "&amp;H452&amp;"  where lab_id = "&amp;A452</f>
+        <f t="shared" ref="N452:N500" si="7">"update lab set lab =  " &amp;C452&amp; " , country =  "&amp;H452&amp;"  where lab_id = "&amp;A452</f>
         <v>update lab set lab =  National Institute of Radiological Sciences , country =    where lab_id = 453</v>
       </c>
     </row>
-    <row r="453" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A453">
         <v>454</v>
       </c>
@@ -15140,11 +15152,11 @@
         <v>48</v>
       </c>
       <c r="N453" t="str">
-        <f>"update lab set lab =  " &amp;C453&amp; " , country =  "&amp;H453&amp;"  where lab_id = "&amp;A453</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Department of Chemistry and Biochemistry - University of Mississippi , country =    where lab_id = 454</v>
       </c>
     </row>
-    <row r="454" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A454">
         <v>455</v>
       </c>
@@ -15164,11 +15176,11 @@
         <v>48</v>
       </c>
       <c r="N454" t="str">
-        <f>"update lab set lab =  " &amp;C454&amp; " , country =  "&amp;H454&amp;"  where lab_id = "&amp;A454</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Marine Science Department - University of Connecticut , country =    where lab_id = 455</v>
       </c>
     </row>
-    <row r="455" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A455">
         <v>456</v>
       </c>
@@ -15188,11 +15200,11 @@
         <v>856</v>
       </c>
       <c r="N455" t="str">
-        <f>"update lab set lab =  " &amp;C455&amp; " , country =  "&amp;H455&amp;"  where lab_id = "&amp;A455</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Ege University - Institute of Nuclear Sciences , country =    where lab_id = 456</v>
       </c>
     </row>
-    <row r="456" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A456">
         <v>457</v>
       </c>
@@ -15212,11 +15224,11 @@
         <v>282</v>
       </c>
       <c r="N456" t="str">
-        <f>"update lab set lab =  " &amp;C456&amp; " , country =  "&amp;H456&amp;"  where lab_id = "&amp;A456</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Aix-Marseille University - Mediterranean Institute of Oceanography , country =    where lab_id = 457</v>
       </c>
     </row>
-    <row r="457" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A457">
         <v>458</v>
       </c>
@@ -15233,11 +15245,11 @@
         <v>15</v>
       </c>
       <c r="N457" t="str">
-        <f>"update lab set lab =  " &amp;C457&amp; " , country =  "&amp;H457&amp;"  where lab_id = "&amp;A457</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  International Laboratory of Marine Radioactivity, Musée Océanographique , country =    where lab_id = 458</v>
       </c>
     </row>
-    <row r="458" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A458">
         <v>459</v>
       </c>
@@ -15254,11 +15266,11 @@
         <v>177</v>
       </c>
       <c r="N458" t="str">
-        <f>"update lab set lab =  " &amp;C458&amp; " , country =  "&amp;H458&amp;"  where lab_id = "&amp;A458</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Department of Bio-Medical Physics - University of Aberdeen , country =    where lab_id = 459</v>
       </c>
     </row>
-    <row r="459" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A459">
         <v>460</v>
       </c>
@@ -15281,11 +15293,11 @@
         <v>48</v>
       </c>
       <c r="N459" t="str">
-        <f>"update lab set lab =  " &amp;C459&amp; " , country =  "&amp;H459&amp;"  where lab_id = "&amp;A459</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Argonne National Laboratory , country =    where lab_id = 460</v>
       </c>
     </row>
-    <row r="460" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A460">
         <v>461</v>
       </c>
@@ -15305,11 +15317,11 @@
         <v>48</v>
       </c>
       <c r="N460" t="str">
-        <f>"update lab set lab =  " &amp;C460&amp; " , country =  "&amp;H460&amp;"  where lab_id = "&amp;A460</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  State University of New York - Marine Sciences Research Center , country =    where lab_id = 461</v>
       </c>
     </row>
-    <row r="461" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A461">
         <v>462</v>
       </c>
@@ -15329,11 +15341,11 @@
         <v>425</v>
       </c>
       <c r="N461" t="str">
-        <f>"update lab set lab =  " &amp;C461&amp; " , country =  "&amp;H461&amp;"  where lab_id = "&amp;A461</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  HCMR Hellenic Centre for Marine Research , country =    where lab_id = 462</v>
       </c>
     </row>
-    <row r="462" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A462">
         <v>463</v>
       </c>
@@ -15350,11 +15362,11 @@
         <v>966</v>
       </c>
       <c r="N462" t="str">
-        <f>"update lab set lab =  " &amp;C462&amp; " , country =  "&amp;H462&amp;"  where lab_id = "&amp;A462</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Malaysian Nuclear Agency , country =    where lab_id = 463</v>
       </c>
     </row>
-    <row r="463" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A463">
         <v>464</v>
       </c>
@@ -15374,11 +15386,11 @@
         <v>456</v>
       </c>
       <c r="N463" t="str">
-        <f>"update lab set lab =  " &amp;C463&amp; " , country =  "&amp;H463&amp;"  where lab_id = "&amp;A463</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Marine Radioecology Group - Center for Radiation Safety Technology and Metrology - National Nuclear Energy Agency of Indonesia _BATAN_ , country =    where lab_id = 464</v>
       </c>
     </row>
-    <row r="464" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A464">
         <v>465</v>
       </c>
@@ -15395,11 +15407,11 @@
         <v>505</v>
       </c>
       <c r="N464" t="str">
-        <f>"update lab set lab =  " &amp;C464&amp; " , country =  "&amp;H464&amp;"  where lab_id = "&amp;A464</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Fukushima University , country =    where lab_id = 465</v>
       </c>
     </row>
-    <row r="465" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A465">
         <v>466</v>
       </c>
@@ -15419,11 +15431,11 @@
         <v>739</v>
       </c>
       <c r="N465" t="str">
-        <f>"update lab set lab =  " &amp;C465&amp; " , country =  "&amp;H465&amp;"  where lab_id = "&amp;A465</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  State University of Novi Pazar , country =    where lab_id = 466</v>
       </c>
     </row>
-    <row r="466" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A466">
         <v>467</v>
       </c>
@@ -15440,11 +15452,11 @@
         <v>335</v>
       </c>
       <c r="N466" t="str">
-        <f>"update lab set lab =  " &amp;C466&amp; " , country =  "&amp;H466&amp;"  where lab_id = "&amp;A466</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Laboratoire d Etude et de Suivi  de l Environnement , country =    where lab_id = 467</v>
       </c>
     </row>
-    <row r="467" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A467">
         <v>468</v>
       </c>
@@ -15461,11 +15473,11 @@
         <v>537</v>
       </c>
       <c r="N467" t="str">
-        <f>"update lab set lab =  " &amp;C467&amp; " , country =  "&amp;H467&amp;"  where lab_id = "&amp;A467</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Korea Institute of Ocean Science &amp; Technology , country =    where lab_id = 468</v>
       </c>
     </row>
-    <row r="468" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A468">
         <v>469</v>
       </c>
@@ -15482,11 +15494,11 @@
         <v>966</v>
       </c>
       <c r="N468" t="str">
-        <f>"update lab set lab =  " &amp;C468&amp; " , country =  "&amp;H468&amp;"  where lab_id = "&amp;A468</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Universiti Kebangsaan Malaysia , country =    where lab_id = 469</v>
       </c>
     </row>
-    <row r="469" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A469">
         <v>470</v>
       </c>
@@ -15506,11 +15518,11 @@
         <v>843</v>
       </c>
       <c r="N469" t="str">
-        <f>"update lab set lab =  " &amp;C469&amp; " , country =  "&amp;H469&amp;"  where lab_id = "&amp;A469</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Ongkarak Nuclear Research Center - Thailand Institute of Nuclear Technology , country =    where lab_id = 470</v>
       </c>
     </row>
-    <row r="470" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A470">
         <v>471</v>
       </c>
@@ -15527,11 +15539,11 @@
         <v>765</v>
       </c>
       <c r="N470" t="str">
-        <f>"update lab set lab =  " &amp;C470&amp; " , country =  "&amp;H470&amp;"  where lab_id = "&amp;A470</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Department of Physics - Universidad de Las Palmas de Gran Canaria , country =    where lab_id = 471</v>
       </c>
     </row>
-    <row r="471" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A471">
         <v>472</v>
       </c>
@@ -15551,11 +15563,11 @@
         <v>128</v>
       </c>
       <c r="N471" t="str">
-        <f>"update lab set lab =  " &amp;C471&amp; " , country =  "&amp;H471&amp;"  where lab_id = "&amp;A471</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Department of Chemistry - Simon Fraser University , country =    where lab_id = 472</v>
       </c>
     </row>
-    <row r="472" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A472">
         <v>473</v>
       </c>
@@ -15575,11 +15587,11 @@
         <v>505</v>
       </c>
       <c r="N472" t="str">
-        <f>"update lab set lab =  " &amp;C472&amp; " , country =  "&amp;H472&amp;"  where lab_id = "&amp;A472</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Iryo Sosei University _former Iwaki Meisei University_ , country =    where lab_id = 473</v>
       </c>
     </row>
-    <row r="473" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A473">
         <v>474</v>
       </c>
@@ -15596,11 +15608,11 @@
         <v>505</v>
       </c>
       <c r="N473" t="str">
-        <f>"update lab set lab =  " &amp;C473&amp; " , country =  "&amp;H473&amp;"  where lab_id = "&amp;A473</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Kobe University , country =    where lab_id = 474</v>
       </c>
     </row>
-    <row r="474" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A474">
         <v>475</v>
       </c>
@@ -15620,11 +15632,11 @@
         <v>505</v>
       </c>
       <c r="N474" t="str">
-        <f>"update lab set lab =  " &amp;C474&amp; " , country =  "&amp;H474&amp;"  where lab_id = "&amp;A474</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Mutsu Establishment - Japan Atomic Energy Agency , country =    where lab_id = 475</v>
       </c>
     </row>
-    <row r="475" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A475">
         <v>476</v>
       </c>
@@ -15641,11 +15653,11 @@
         <v>505</v>
       </c>
       <c r="N475" t="str">
-        <f>"update lab set lab =  " &amp;C475&amp; " , country =  "&amp;H475&amp;"  where lab_id = "&amp;A475</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Niigata Prefectural Institute of Environmental Radiation Monitoring , country =    where lab_id = 476</v>
       </c>
     </row>
-    <row r="476" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A476">
         <v>477</v>
       </c>
@@ -15662,11 +15674,11 @@
         <v>505</v>
       </c>
       <c r="N476" t="str">
-        <f>"update lab set lab =  " &amp;C476&amp; " , country =  "&amp;H476&amp;"  where lab_id = "&amp;A476</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Miyagi Prefecture Environmental Radiation Monitoring Center _former Environmental Radioactivity Research Institute of Miyagi_ , country =    where lab_id = 477</v>
       </c>
     </row>
-    <row r="477" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A477">
         <v>478</v>
       </c>
@@ -15683,11 +15695,11 @@
         <v>505</v>
       </c>
       <c r="N477" t="str">
-        <f>"update lab set lab =  " &amp;C477&amp; " , country =  "&amp;H477&amp;"  where lab_id = "&amp;A477</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Faculty of Engineering - Hokkaido University , country =    where lab_id = 478</v>
       </c>
     </row>
-    <row r="478" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A478">
         <v>479</v>
       </c>
@@ -15704,11 +15716,11 @@
         <v>505</v>
       </c>
       <c r="N478" t="str">
-        <f>"update lab set lab =  " &amp;C478&amp; " , country =  "&amp;H478&amp;"  where lab_id = "&amp;A478</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Fukushima Agricultural Technology Centre , country =    where lab_id = 479</v>
       </c>
     </row>
-    <row r="479" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A479">
         <v>480</v>
       </c>
@@ -15728,11 +15740,11 @@
         <v>505</v>
       </c>
       <c r="N479" t="str">
-        <f>"update lab set lab =  " &amp;C479&amp; " , country =  "&amp;H479&amp;"  where lab_id = "&amp;A479</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  National Research Institute of Fisheries Science _former Tokai Regional Fisheries Research Laboratory_, Japan Fisheries Research and Education Agency , country =    where lab_id = 480</v>
       </c>
     </row>
-    <row r="480" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A480">
         <v>481</v>
       </c>
@@ -15752,11 +15764,11 @@
         <v>505</v>
       </c>
       <c r="N480" t="str">
-        <f>"update lab set lab =  " &amp;C480&amp; " , country =  "&amp;H480&amp;"  where lab_id = "&amp;A480</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Japan Fisheries Research and Education Agency _former Fisheries Research Agency, and National Fisheries University_ , country =    where lab_id = 481</v>
       </c>
     </row>
-    <row r="481" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A481">
         <v>482</v>
       </c>
@@ -15776,11 +15788,11 @@
         <v>505</v>
       </c>
       <c r="N481" t="str">
-        <f>"update lab set lab =  " &amp;C481&amp; " , country =  "&amp;H481&amp;"  where lab_id = "&amp;A481</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  National Institute of Radiological Sciences , country =    where lab_id = 482</v>
       </c>
     </row>
-    <row r="482" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A482">
         <v>483</v>
       </c>
@@ -15797,11 +15809,11 @@
         <v>505</v>
       </c>
       <c r="N482" t="str">
-        <f>"update lab set lab =  " &amp;C482&amp; " , country =  "&amp;H482&amp;"  where lab_id = "&amp;A482</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Fukushima Prefectural Fisheries Experimental Station , country =    where lab_id = 483</v>
       </c>
     </row>
-    <row r="483" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A483">
         <v>484</v>
       </c>
@@ -15821,11 +15833,11 @@
         <v>109</v>
       </c>
       <c r="N483" t="str">
-        <f>"update lab set lab =  " &amp;C483&amp; " , country =  "&amp;H483&amp;"  where lab_id = "&amp;A483</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Universidade Federal Fluminense - InInstituto de Biologia , country =    where lab_id = 484</v>
       </c>
     </row>
-    <row r="484" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A484">
         <v>485</v>
       </c>
@@ -15842,11 +15854,11 @@
         <v>1448</v>
       </c>
       <c r="N484" t="str">
-        <f>"update lab set lab =  " &amp;C484&amp; " , country =  "&amp;H484&amp;"  where lab_id = "&amp;A484</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Sudan Atomic Energy Commission , country =    where lab_id = 485</v>
       </c>
     </row>
-    <row r="485" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A485">
         <v>486</v>
       </c>
@@ -15860,11 +15872,11 @@
         <v>400</v>
       </c>
       <c r="N485" t="str">
-        <f>"update lab set lab =  " &amp;C485&amp; " , country =  "&amp;H485&amp;"  where lab_id = "&amp;A485</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Duy Tan University - Institute of Research and Development , country =    where lab_id = 486</v>
       </c>
     </row>
-    <row r="486" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A486">
         <v>487</v>
       </c>
@@ -15881,11 +15893,11 @@
         <v>282</v>
       </c>
       <c r="N486" t="str">
-        <f>"update lab set lab =  " &amp;C486&amp; " , country =  "&amp;H486&amp;"  where lab_id = "&amp;A486</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire - Laboratoire de Radioécologie de Cherbourg-Octeville , country =    where lab_id = 487</v>
       </c>
     </row>
-    <row r="487" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A487">
         <v>488</v>
       </c>
@@ -15899,11 +15911,11 @@
         <v>1071</v>
       </c>
       <c r="N487" t="str">
-        <f>"update lab set lab =  " &amp;C487&amp; " , country =  "&amp;H487&amp;"  where lab_id = "&amp;A487</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  University of the Faroe Islands , country =    where lab_id = 488</v>
       </c>
     </row>
-    <row r="488" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A488">
         <v>489</v>
       </c>
@@ -15920,11 +15932,11 @@
         <v>630</v>
       </c>
       <c r="N488" t="str">
-        <f>"update lab set lab =  " &amp;C488&amp; " , country =  "&amp;H488&amp;"  where lab_id = "&amp;A488</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Norwegian University of Science and Technology - Department of Biology , country =    where lab_id = 489</v>
       </c>
     </row>
-    <row r="489" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A489">
         <v>490</v>
       </c>
@@ -15941,11 +15953,11 @@
         <v>99</v>
       </c>
       <c r="N489" t="str">
-        <f>"update lab set lab =  " &amp;C489&amp; " , country =  "&amp;H489&amp;"  where lab_id = "&amp;A489</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  University of Gothenburg - Department of Biological and Environmental Sciences , country =    where lab_id = 490</v>
       </c>
     </row>
-    <row r="490" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A490">
         <v>491</v>
       </c>
@@ -15962,11 +15974,11 @@
         <v>1071</v>
       </c>
       <c r="N490" t="str">
-        <f>"update lab set lab =  " &amp;C490&amp; " , country =  "&amp;H490&amp;"  where lab_id = "&amp;A490</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Risø National Laboratory , country =    where lab_id = 491</v>
       </c>
     </row>
-    <row r="491" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A491">
         <v>492</v>
       </c>
@@ -15983,11 +15995,11 @@
         <v>485</v>
       </c>
       <c r="N491" t="str">
-        <f>"update lab set lab =  " &amp;C491&amp; " , country =  "&amp;H491&amp;"  where lab_id = "&amp;A491</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Urbino University - Institute of General Chemistry , country =    where lab_id = 492</v>
       </c>
     </row>
-    <row r="492" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A492">
         <v>493</v>
       </c>
@@ -16001,11 +16013,11 @@
         <v>31</v>
       </c>
       <c r="N492" t="str">
-        <f>"update lab set lab =  " &amp;C492&amp; " , country =  "&amp;H492&amp;"  where lab_id = "&amp;A492</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  University of Gdańsk - Faculty of Chemistry , country =    where lab_id = 493</v>
       </c>
     </row>
-    <row r="493" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A493">
         <v>494</v>
       </c>
@@ -16022,11 +16034,11 @@
         <v>622</v>
       </c>
       <c r="N493" t="str">
-        <f>"update lab set lab =  " &amp;C493&amp; " , country =  "&amp;H493&amp;"  where lab_id = "&amp;A493</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  University of Otago - Department of Chemistry , country =    where lab_id = 494</v>
       </c>
     </row>
-    <row r="494" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A494">
         <v>495</v>
       </c>
@@ -16043,11 +16055,11 @@
         <v>31</v>
       </c>
       <c r="N494" t="str">
-        <f>"update lab set lab =  " &amp;C494&amp; " , country =  "&amp;H494&amp;"  where lab_id = "&amp;A494</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  University of Silesia - Institute of Physics , country =    where lab_id = 495</v>
       </c>
     </row>
-    <row r="495" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A495">
         <v>496</v>
       </c>
@@ -16058,11 +16070,11 @@
         <v>765</v>
       </c>
       <c r="N495" t="str">
-        <f>"update lab set lab =  " &amp;C495&amp; " , country =  "&amp;H495&amp;"  where lab_id = "&amp;A495</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Centro Nacional de Aceleradores _CNA_, Universidad de Sevilla, Spain , country =    where lab_id = 496</v>
       </c>
     </row>
-    <row r="496" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A496">
         <v>497</v>
       </c>
@@ -16073,11 +16085,11 @@
         <v>765</v>
       </c>
       <c r="N496" t="str">
-        <f>"update lab set lab =  " &amp;C496&amp; " , country =  "&amp;H496&amp;"  where lab_id = "&amp;A496</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Universidad de Sevilla, Spain , country =    where lab_id = 497</v>
       </c>
     </row>
-    <row r="497" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A497">
         <v>498</v>
       </c>
@@ -16088,11 +16100,11 @@
         <v>1071</v>
       </c>
       <c r="N497" t="str">
-        <f>"update lab set lab =  " &amp;C497&amp; " , country =  "&amp;H497&amp;"  where lab_id = "&amp;A497</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  DTU Environment , country =    where lab_id = 498</v>
       </c>
     </row>
-    <row r="498" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A498">
         <v>499</v>
       </c>
@@ -16106,11 +16118,11 @@
         <v>630</v>
       </c>
       <c r="N498" t="str">
-        <f>"update lab set lab =  " &amp;C498&amp; " , country =  "&amp;H498&amp;"  where lab_id = "&amp;A498</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Norwegian Radiation and Nuclear Safety Authority , country =    where lab_id = 499</v>
       </c>
     </row>
-    <row r="499" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A499">
         <v>500</v>
       </c>
@@ -16124,11 +16136,11 @@
         <v>282</v>
       </c>
       <c r="N499" t="str">
-        <f>"update lab set lab =  " &amp;C499&amp; " , country =  "&amp;H499&amp;"  where lab_id = "&amp;A499</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Institut de Radioprotection et de Sûreté Nucléaire   LSE -  SAME _ALOKA_ , country =    where lab_id = 500</v>
       </c>
     </row>
-    <row r="500" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A500">
         <v>501</v>
       </c>
@@ -16142,11 +16154,11 @@
         <v>177</v>
       </c>
       <c r="N500" t="str">
-        <f>"update lab set lab =  " &amp;C500&amp; " , country =  "&amp;H500&amp;"  where lab_id = "&amp;A500</f>
+        <f t="shared" si="7"/>
         <v>update lab set lab =  Sellafield Ltd , country =    where lab_id = 501</v>
       </c>
     </row>
-    <row r="501" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A501">
         <v>502</v>
       </c>
@@ -16160,7 +16172,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="502" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A502">
         <v>503</v>
       </c>
@@ -16174,8 +16186,19 @@
         <v>1448</v>
       </c>
     </row>
+    <row r="503" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A503">
+        <v>504</v>
+      </c>
+      <c r="B503" t="s">
+        <v>1610</v>
+      </c>
+      <c r="C503" t="s">
+        <v>1611</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K519"/>
+  <autoFilter ref="A1:K519" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -16191,6 +16214,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f3c01d95-e195-4940-9fb4-afa395d98e0b">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="77012c7d-7b27-41e5-8843-0f8877a4d830" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006C266C02A97D1D41B60FC5BB4AB3B561" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c0803d2d8cf8a508143be379ec3e9db2">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3c01d95-e195-4940-9fb4-afa395d98e0b" xmlns:ns3="77012c7d-7b27-41e5-8843-0f8877a4d830" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d5c96b8183d092d730d8e1cf5f89dc9d" ns2:_="" ns3:_="">
     <xsd:import namespace="f3c01d95-e195-4940-9fb4-afa395d98e0b"/>
@@ -16425,17 +16459,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f3c01d95-e195-4940-9fb4-afa395d98e0b">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="77012c7d-7b27-41e5-8843-0f8877a4d830" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{70630E28-52C0-4D0E-9782-67C868EE0408}">
   <ds:schemaRefs>
@@ -16445,6 +16468,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CA1F0F8-DC4D-4181-A3DE-03D28F858DC2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f3c01d95-e195-4940-9fb4-afa395d98e0b"/>
+    <ds:schemaRef ds:uri="77012c7d-7b27-41e5-8843-0f8877a4d830"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87FB7588-012B-4BE5-AB16-EF02AE7FBC5A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -16461,15 +16495,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CA1F0F8-DC4D-4181-A3DE-03D28F858DC2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="f3c01d95-e195-4940-9fb4-afa395d98e0b"/>
-    <ds:schemaRef ds:uri="77012c7d-7b27-41e5-8843-0f8877a4d830"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>